--- a/output/pdf_financials_xlsx/CTM.xlsx
+++ b/output/pdf_financials_xlsx/CTM.xlsx
@@ -5408,49 +5408,49 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>1.722857</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.760212</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.189889</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.21781</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.268352</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.125023</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>0.156367</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>0.147381</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>0.070044</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>0.04764</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>2.932874</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>2.497594</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>11.698235</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>2.877346</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>3.413487</v>
       </c>
     </row>
     <row r="93">
@@ -8772,7 +8772,11 @@
           <t>Reserves (Note 12)</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>-</t>
@@ -9440,7 +9444,11 @@
           <t>Reserves (Note 10)</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E21" s="5" t="n">
         <v>1.722857</v>
       </c>
@@ -10209,7 +10217,11 @@
           <t>Reserves (Note 10)</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E30" t="inlineStr">
         <is>
           <t>-</t>
@@ -11004,7 +11016,11 @@
           <t>Reserves (Note 10)</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr"/>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E39" t="inlineStr">
         <is>
           <t>-</t>
@@ -12632,7 +12648,11 @@
           <t>Reserves (Note 11)</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr"/>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E57" t="inlineStr">
         <is>
           <t>-</t>
@@ -14092,7 +14112,11 @@
           <t>Reserves (Note 10) 760,212</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr"/>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E73" s="5" t="n">
         <v>1.827769</v>
       </c>

--- a/output/pdf_financials_xlsx/CTM.xlsx
+++ b/output/pdf_financials_xlsx/CTM.xlsx
@@ -987,13 +987,13 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.029443</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.001534</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.013911</v>
       </c>
       <c r="E12" s="3" t="n">
         <v>0</v>
@@ -1002,19 +1002,19 @@
         <v>0</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.001344</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.000166</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.000279</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>6.2e-05</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>5.8e-05</v>
       </c>
       <c r="L12" s="3" t="n">
         <v>0</v>
@@ -1023,13 +1023,13 @@
         <v>0</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>0.009669000000000001</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>0.035358</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>0.052945</v>
       </c>
     </row>
     <row r="13">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-42.420437</v>
+        <v>-42.44988</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-1.182691</v>
+        <v>-1.184225</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-2.378742</v>
+        <v>-2.392653</v>
       </c>
       <c r="E27" s="3" t="n">
         <v>-8.677626999999999</v>
@@ -1864,19 +1864,19 @@
         <v>-1.656563</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-0.954315</v>
+        <v>-0.955659</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-0.963432</v>
+        <v>-0.963598</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-0.6026319999999999</v>
+        <v>-0.602911</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>0.231072</v>
+        <v>0.23101</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-0.152376</v>
+        <v>-0.152434</v>
       </c>
       <c r="L27" s="3" t="n">
         <v>-4.798703</v>
@@ -1885,13 +1885,13 @@
         <v>-3.638684</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-1.01337</v>
+        <v>-1.023039</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-3.239012</v>
+        <v>-3.27437</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-5.075306</v>
+        <v>-5.128251</v>
       </c>
     </row>
     <row r="28">
@@ -1953,13 +1953,13 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-42.351279</v>
+        <v>-42.380722</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-1.129927</v>
+        <v>-1.131461</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-2.341213</v>
+        <v>-2.355124</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>-8.677626999999999</v>
@@ -1968,19 +1968,19 @@
         <v>-1.656563</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-0.954315</v>
+        <v>-0.955659</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-0.963432</v>
+        <v>-0.963598</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-0.6026319999999999</v>
+        <v>-0.602911</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>0.231072</v>
+        <v>0.23101</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-0.152376</v>
+        <v>-0.152434</v>
       </c>
       <c r="L29" s="3" t="n">
         <v>-4.798703</v>
@@ -1989,13 +1989,13 @@
         <v>-3.638684</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-1.01337</v>
+        <v>-1.023039</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-3.239012</v>
+        <v>-3.27437</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-5.075306</v>
+        <v>-5.128251</v>
       </c>
     </row>
     <row r="30">
@@ -2228,40 +2228,40 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.459768</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>1.615231</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.958244</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.185994</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.831975</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.482977</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.044857</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.031283</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.009894999999999999</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.0103</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>3.059252</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.653679</v>
       </c>
       <c r="N34" s="3" t="n">
         <v>1.821239</v>
@@ -2332,40 +2332,40 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.459768</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>1.615231</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.958244</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0.6</v>
+        <v>0.785994</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0.036712</v>
+        <v>0.868687</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0.043897</v>
+        <v>0.526874</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0.02789</v>
+        <v>0.07274700000000001</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0.002998</v>
+        <v>0.034281</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0.001898</v>
+        <v>0.011793</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0.00069</v>
+        <v>0.01099</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0.000897</v>
+        <v>3.060149</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>6.9e-05</v>
+        <v>0.653748</v>
       </c>
       <c r="N36" s="3" t="n">
         <v>1.82136</v>
@@ -2956,40 +2956,40 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>2.963688</v>
+        <v>2.50392</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.545313</v>
+        <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.959961</v>
+        <v>0.001717</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.187781</v>
+        <v>0.001787</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.8336750000000001</v>
+        <v>0.0017</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.482977</v>
+        <v>0</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.044857</v>
+        <v>0</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.031283</v>
+        <v>0</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.009894999999999999</v>
+        <v>0</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.02286</v>
+        <v>0.01256</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>3.0971</v>
+        <v>0.037848</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.653679</v>
+        <v>0</v>
       </c>
       <c r="N48" s="3" t="n">
         <v>0.060917</v>
@@ -9525,7 +9525,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E22" s="5" t="n">
@@ -13192,7 +13192,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E63" s="5" t="n">
@@ -32152,7 +32152,7 @@
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
@@ -38103,7 +38103,7 @@
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E342" t="inlineStr">
@@ -38928,7 +38928,7 @@
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E351" s="5" t="n">

--- a/output/pdf_financials_xlsx/CTM.xlsx
+++ b/output/pdf_financials_xlsx/CTM.xlsx
@@ -886,7 +886,7 @@
         <v>0.877555</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.199243</v>
+        <v>0.856069</v>
       </c>
       <c r="F10" s="3" t="n">
         <v>1.51331</v>
@@ -938,7 +938,7 @@
         <v>-0.877555</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>-0.199243</v>
+        <v>-0.856069</v>
       </c>
       <c r="F11" s="3" t="n">
         <v>-1.51331</v>
@@ -996,7 +996,7 @@
         <v>0.013911</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.004406</v>
       </c>
       <c r="F12" s="3" t="n">
         <v>0</v>
@@ -1247,7 +1247,7 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>0.737</v>
+        <v>-0.737</v>
       </c>
       <c r="C17" s="3" t="n">
         <v>-0.126858</v>
@@ -1858,7 +1858,7 @@
         <v>-2.392653</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-8.677626999999999</v>
+        <v>-8.682033000000001</v>
       </c>
       <c r="F27" s="3" t="n">
         <v>-1.656563</v>
@@ -1910,7 +1910,7 @@
         <v>0.037529</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>0</v>
+        <v>0.02841</v>
       </c>
       <c r="F28" s="3" t="n">
         <v>0</v>
@@ -1962,7 +1962,7 @@
         <v>-2.355124</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-8.677626999999999</v>
+        <v>-8.653623</v>
       </c>
       <c r="F29" s="3" t="n">
         <v>-1.656563</v>
@@ -4029,46 +4029,46 @@
         <v>0</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.0225</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.015</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>0.015</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>0.06167</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0</v>
+        <v>0.0125</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0</v>
+        <v>0.0175</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>0</v>
+        <v>0.0175</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="M67" s="3" t="n">
-        <v>0</v>
+        <v>0.031087</v>
       </c>
       <c r="N67" s="3" t="n">
-        <v>0</v>
+        <v>0.097</v>
       </c>
       <c r="O67" s="3" t="n">
-        <v>0</v>
+        <v>0.214384</v>
       </c>
       <c r="P67" s="3" t="n">
-        <v>0</v>
+        <v>0.233875</v>
       </c>
     </row>
     <row r="68">
@@ -6601,19 +6601,19 @@
         <v>0</v>
       </c>
       <c r="F115" s="3" t="n">
-        <v>0</v>
+        <v>0.24791</v>
       </c>
       <c r="G115" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H115" s="3" t="n">
-        <v>0</v>
+        <v>0.06501999999999999</v>
       </c>
       <c r="I115" s="3" t="n">
-        <v>0</v>
+        <v>0.031675</v>
       </c>
       <c r="J115" s="3" t="n">
-        <v>0</v>
+        <v>0.00245</v>
       </c>
       <c r="K115" s="3" t="n">
         <v>0</v>
@@ -6628,10 +6628,10 @@
         <v>0</v>
       </c>
       <c r="O115" s="3" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="P115" s="3" t="n">
-        <v>0</v>
+        <v>0.545455</v>
       </c>
     </row>
     <row r="116">
@@ -7731,7 +7731,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S357"/>
+  <dimension ref="A1:S369"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -15277,7 +15277,11 @@
           <t>Proceeds received from sale of marketable securities</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr"/>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E86" t="inlineStr">
         <is>
           <t>-</t>
@@ -15380,10 +15384,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H87" s="5" t="n">
+        <v>-0.057139</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
@@ -18438,10 +18440,8 @@
       <c r="G121" s="5" t="n">
         <v>-0.002774</v>
       </c>
-      <c r="H121" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H121" s="5" t="n">
+        <v>0.008388</v>
       </c>
       <c r="I121" t="inlineStr">
         <is>
@@ -20881,10 +20881,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H148" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H148" s="5" t="n">
+        <v>0.087187</v>
       </c>
       <c r="I148" s="5" t="n">
         <v>0.04901</v>
@@ -21225,10 +21223,8 @@
       <c r="G152" s="5" t="n">
         <v>0.008357</v>
       </c>
-      <c r="H152" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H152" s="5" t="n">
+        <v>-6.999999999999999e-05</v>
       </c>
       <c r="I152" t="inlineStr">
         <is>
@@ -21500,10 +21496,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H155" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H155" s="5" t="n">
+        <v>-0.007139</v>
       </c>
       <c r="I155" t="inlineStr">
         <is>
@@ -24565,15 +24559,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G189" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H189" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G189" s="5" t="n">
+        <v>1.748047</v>
+      </c>
+      <c r="H189" s="5" t="n">
+        <v>8.375658</v>
       </c>
       <c r="I189" t="inlineStr">
         <is>
@@ -25009,7 +24999,11 @@
           <t>Proceeds on sale of marketable securities</t>
         </is>
       </c>
-      <c r="D194" t="inlineStr"/>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E194" t="inlineStr">
         <is>
           <t>-</t>
@@ -27248,10 +27242,8 @@
       <c r="G219" s="5" t="n">
         <v>-0.656987</v>
       </c>
-      <c r="H219" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H219" s="5" t="n">
+        <v>-0.77225</v>
       </c>
       <c r="I219" s="5" t="n">
         <v>0.645981</v>
@@ -27331,10 +27323,8 @@
       <c r="G220" s="5" t="n">
         <v>1.615231</v>
       </c>
-      <c r="H220" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H220" s="5" t="n">
+        <v>0.958244</v>
       </c>
       <c r="I220" s="5" t="n">
         <v>0.185994</v>
@@ -27414,10 +27404,8 @@
       <c r="G221" s="5" t="n">
         <v>0.958244</v>
       </c>
-      <c r="H221" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H221" s="5" t="n">
+        <v>0.185994</v>
       </c>
       <c r="I221" s="5" t="n">
         <v>0.831975</v>
@@ -27584,10 +27572,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H223" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H223" s="5" t="n">
+        <v>-0.09465</v>
       </c>
       <c r="I223" s="5" t="n">
         <v>0.192781</v>
@@ -29501,10 +29487,8 @@
       <c r="G244" s="5" t="n">
         <v>0.037529</v>
       </c>
-      <c r="H244" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H244" s="5" t="n">
+        <v>0.02841</v>
       </c>
       <c r="I244" t="inlineStr">
         <is>
@@ -29575,7 +29559,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Write-off of exploration deposits</t>
+          <t>Write-down of mineral deposits</t>
         </is>
       </c>
       <c r="D245" t="inlineStr"/>
@@ -29666,23 +29650,27 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Write-off of mineral properties</t>
+          <t>Write-down of equipment</t>
         </is>
       </c>
       <c r="D246" t="inlineStr"/>
-      <c r="E246" s="5" t="n">
-        <v>40.968246</v>
-      </c>
-      <c r="F246" s="5" t="n">
-        <v>0.403033</v>
-      </c>
-      <c r="G246" s="5" t="n">
-        <v>1.748047</v>
-      </c>
-      <c r="H246" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H246" s="5" t="n">
+        <v>0.100306</v>
       </c>
       <c r="I246" t="inlineStr">
         <is>
@@ -29748,12 +29736,12 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital items</t>
+          <t>Items not affecting cash</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>(Increase) decrease in exploration advances</t>
+          <t>Gain on sale of mineral properties</t>
         </is>
       </c>
       <c r="D247" t="inlineStr"/>
@@ -29762,18 +29750,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F247" s="5" t="n">
-        <v>0.0163</v>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H247" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H247" s="5" t="n">
+        <v>-0.55535</v>
       </c>
       <c r="I247" t="inlineStr">
         <is>
@@ -29861,10 +29849,8 @@
       <c r="G248" s="5" t="n">
         <v>-0.09940400000000001</v>
       </c>
-      <c r="H248" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H248" s="5" t="n">
+        <v>-0.037363</v>
       </c>
       <c r="I248" t="inlineStr">
         <is>
@@ -29952,10 +29938,8 @@
       <c r="G249" s="5" t="n">
         <v>-0.656987</v>
       </c>
-      <c r="H249" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H249" s="5" t="n">
+        <v>-0.765111</v>
       </c>
       <c r="I249" t="inlineStr">
         <is>
@@ -30021,12 +30005,12 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Cash flows from financing activities</t>
+          <t>Cash flows from investing activities</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Loan proceeds received</t>
+          <t>Disposition of mineral properties</t>
         </is>
       </c>
       <c r="D250" t="inlineStr"/>
@@ -30035,18 +30019,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F250" s="5" t="n">
-        <v>0.125</v>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H250" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H250" s="5" t="n">
+        <v>0.05</v>
       </c>
       <c r="I250" t="inlineStr">
         <is>
@@ -30112,12 +30096,12 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Cash flows from financing activities</t>
+          <t>Items not affecting cash</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Repayment of loan proceeds</t>
+          <t>Write-off of exploration deposits</t>
         </is>
       </c>
       <c r="D251" t="inlineStr"/>
@@ -30126,13 +30110,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F251" s="5" t="n">
-        <v>-0.125</v>
-      </c>
-      <c r="G251" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G251" s="5" t="n">
+        <v>0.03</v>
       </c>
       <c r="H251" t="inlineStr">
         <is>
@@ -30203,27 +30187,23 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Cash flows from investing activities</t>
+          <t>Items not affecting cash</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>(Acquisition) disposition of equipment</t>
+          <t>Write-off of mineral properties</t>
         </is>
       </c>
       <c r="D252" t="inlineStr"/>
-      <c r="E252" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E252" s="5" t="n">
+        <v>40.968246</v>
       </c>
       <c r="F252" s="5" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="G252" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.403033</v>
+      </c>
+      <c r="G252" s="5" t="n">
+        <v>1.748047</v>
       </c>
       <c r="H252" t="inlineStr">
         <is>
@@ -30294,20 +30274,22 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Cash flows from investing activities</t>
+          <t>Changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Exploration deposits</t>
+          <t>(Increase) decrease in exploration advances</t>
         </is>
       </c>
       <c r="D253" t="inlineStr"/>
-      <c r="E253" s="5" t="n">
-        <v>0.142194</v>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F253" s="5" t="n">
-        <v>0.138088</v>
+        <v>0.0163</v>
       </c>
       <c r="G253" t="inlineStr">
         <is>
@@ -30383,22 +30365,22 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Items not affecting cash</t>
+          <t>Cash flows from financing activities</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Deferred income tax recovery</t>
+          <t>Loan proceeds received</t>
         </is>
       </c>
       <c r="D254" t="inlineStr"/>
-      <c r="E254" s="5" t="n">
-        <v>-0.737</v>
-      </c>
-      <c r="F254" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F254" s="5" t="n">
+        <v>0.125</v>
       </c>
       <c r="G254" t="inlineStr">
         <is>
@@ -30474,20 +30456,22 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Cash flows from investing activities</t>
+          <t>Cash flows from financing activities</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Mineral property expenditures</t>
+          <t>Repayment of loan proceeds</t>
         </is>
       </c>
       <c r="D255" t="inlineStr"/>
-      <c r="E255" s="5" t="n">
-        <v>-1.327111</v>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F255" s="5" t="n">
-        <v>-0.382507</v>
+        <v>-0.125</v>
       </c>
       <c r="G255" t="inlineStr">
         <is>
@@ -30568,17 +30552,17 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Exploration advances</t>
+          <t>(Acquisition) disposition of equipment</t>
         </is>
       </c>
       <c r="D256" t="inlineStr"/>
-      <c r="E256" s="5" t="n">
-        <v>-0.0163</v>
-      </c>
-      <c r="F256" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F256" s="5" t="n">
+        <v>0.015</v>
       </c>
       <c r="G256" t="inlineStr">
         <is>
@@ -30649,97 +30633,115 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Cash flows from investing activities</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Business development $</t>
+          <t>Exploration deposits</t>
         </is>
       </c>
       <c r="D257" t="inlineStr"/>
-      <c r="E257" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F257" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E257" s="5" t="n">
+        <v>0.142194</v>
+      </c>
+      <c r="F257" s="5" t="n">
+        <v>0.138088</v>
       </c>
       <c r="G257" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H257" s="5" t="n">
-        <v>0.011729</v>
-      </c>
-      <c r="I257" s="5" t="n">
-        <v>0.110097</v>
-      </c>
-      <c r="J257" s="5" t="n">
-        <v>0.079901</v>
-      </c>
-      <c r="K257" s="5" t="n">
-        <v>0.005782</v>
-      </c>
-      <c r="L257" s="5" t="n">
-        <v>0.001445</v>
-      </c>
-      <c r="M257" s="5" t="n">
-        <v>0.001952</v>
-      </c>
-      <c r="N257" s="5" t="n">
-        <v>0.001101</v>
-      </c>
-      <c r="O257" s="5" t="n">
-        <v>0.049215</v>
-      </c>
-      <c r="P257" s="5" t="n">
-        <v>0.053286</v>
-      </c>
-      <c r="Q257" s="5" t="n">
-        <v>0.037907</v>
-      </c>
-      <c r="R257" s="5" t="n">
-        <v>0.237856</v>
-      </c>
-      <c r="S257" s="5" t="n">
-        <v>0.323473</v>
+      <c r="H257" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I257" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J257" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K257" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L257" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M257" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N257" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O257" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P257" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q257" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R257" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S257" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Items not affecting cash</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Deferred income tax recovery</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E258" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
+      <c r="E258" s="5" t="n">
+        <v>-0.737</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -30756,66 +30758,84 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I258" s="5" t="n">
-        <v>0.04176</v>
-      </c>
-      <c r="J258" s="5" t="n">
-        <v>0.036725</v>
-      </c>
-      <c r="K258" s="5" t="n">
-        <v>0.03157</v>
-      </c>
-      <c r="L258" s="5" t="n">
-        <v>0.002489</v>
-      </c>
-      <c r="M258" s="5" t="n">
-        <v>0.00237</v>
-      </c>
-      <c r="N258" s="5" t="n">
-        <v>0.010138</v>
-      </c>
-      <c r="O258" s="5" t="n">
-        <v>0.0169</v>
-      </c>
-      <c r="P258" s="5" t="n">
-        <v>0.020434</v>
-      </c>
-      <c r="Q258" s="5" t="n">
-        <v>0.02076</v>
-      </c>
-      <c r="R258" s="5" t="n">
-        <v>0.020999</v>
-      </c>
-      <c r="S258" s="5" t="n">
-        <v>0.021055</v>
+      <c r="I258" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J258" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K258" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L258" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M258" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N258" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O258" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P258" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q258" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R258" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S258" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Cash flows from investing activities</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Legal, audit and accounting</t>
+          <t>Mineral property expenditures</t>
         </is>
       </c>
       <c r="D259" t="inlineStr"/>
-      <c r="E259" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F259" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E259" s="5" t="n">
+        <v>-1.327111</v>
+      </c>
+      <c r="F259" s="5" t="n">
+        <v>-0.382507</v>
       </c>
       <c r="G259" t="inlineStr">
         <is>
@@ -30827,65 +30847,81 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I259" s="5" t="n">
-        <v>0.046795</v>
-      </c>
-      <c r="J259" s="5" t="n">
-        <v>0.063184</v>
-      </c>
-      <c r="K259" s="5" t="n">
-        <v>0.030545</v>
-      </c>
-      <c r="L259" s="5" t="n">
-        <v>0.027115</v>
-      </c>
-      <c r="M259" s="5" t="n">
-        <v>0.029378</v>
-      </c>
-      <c r="N259" s="5" t="n">
-        <v>0.02923</v>
-      </c>
-      <c r="O259" s="5" t="n">
-        <v>0.264219</v>
-      </c>
-      <c r="P259" s="5" t="n">
-        <v>0.065058</v>
-      </c>
-      <c r="Q259" s="5" t="n">
-        <v>0.152942</v>
-      </c>
-      <c r="R259" s="5" t="n">
-        <v>0.101264</v>
-      </c>
-      <c r="S259" s="5" t="n">
-        <v>0.107922</v>
+      <c r="I259" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J259" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K259" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L259" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M259" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N259" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O259" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P259" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q259" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R259" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S259" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Cash flows from investing activities</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Consulting fees (Note 10)</t>
-        </is>
-      </c>
-      <c r="D260" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E260" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Exploration advances</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr"/>
+      <c r="E260" s="5" t="n">
+        <v>-0.0163</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -30947,11 +30983,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="R260" s="5" t="n">
-        <v>0.2176</v>
-      </c>
-      <c r="S260" s="5" t="n">
-        <v>0.08450000000000001</v>
+      <c r="R260" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S260" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="261">
@@ -30967,14 +31007,10 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Office and miscellaneous</t>
-        </is>
-      </c>
-      <c r="D261" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Business development $</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr"/>
       <c r="E261" t="inlineStr">
         <is>
           <t>-</t>
@@ -30985,48 +31021,44 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G261" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H261" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G261" s="5" t="n">
+        <v>0.00678</v>
+      </c>
+      <c r="H261" s="5" t="n">
+        <v>0.011729</v>
       </c>
       <c r="I261" s="5" t="n">
-        <v>0.043192</v>
+        <v>0.110097</v>
       </c>
       <c r="J261" s="5" t="n">
-        <v>0.037462</v>
+        <v>0.079901</v>
       </c>
       <c r="K261" s="5" t="n">
-        <v>0.042719</v>
+        <v>0.005782</v>
       </c>
       <c r="L261" s="5" t="n">
-        <v>0.033811</v>
+        <v>0.001445</v>
       </c>
       <c r="M261" s="5" t="n">
-        <v>0.005157</v>
+        <v>0.001952</v>
       </c>
       <c r="N261" s="5" t="n">
-        <v>0.00268</v>
+        <v>0.001101</v>
       </c>
       <c r="O261" s="5" t="n">
-        <v>0.028774</v>
+        <v>0.049215</v>
       </c>
       <c r="P261" s="5" t="n">
-        <v>0.030904</v>
+        <v>0.053286</v>
       </c>
       <c r="Q261" s="5" t="n">
-        <v>0.045867</v>
+        <v>0.037907</v>
       </c>
       <c r="R261" s="5" t="n">
-        <v>0.018525</v>
+        <v>0.237856</v>
       </c>
       <c r="S261" s="5" t="n">
-        <v>0.07324700000000001</v>
+        <v>0.323473</v>
       </c>
     </row>
     <row r="262">
@@ -31042,7 +31074,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Regulatory and transfer agent fees</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -31060,48 +31092,44 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G262" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H262" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G262" s="5" t="n">
+        <v>0.042998</v>
+      </c>
+      <c r="H262" s="5" t="n">
+        <v>0.043873</v>
       </c>
       <c r="I262" s="5" t="n">
-        <v>0.038921</v>
+        <v>0.04176</v>
       </c>
       <c r="J262" s="5" t="n">
-        <v>0.018067</v>
+        <v>0.036725</v>
       </c>
       <c r="K262" s="5" t="n">
-        <v>0.022613</v>
+        <v>0.03157</v>
       </c>
       <c r="L262" s="5" t="n">
-        <v>0.012261</v>
+        <v>0.002489</v>
       </c>
       <c r="M262" s="5" t="n">
-        <v>0.026781</v>
+        <v>0.00237</v>
       </c>
       <c r="N262" s="5" t="n">
-        <v>0.017254</v>
+        <v>0.010138</v>
       </c>
       <c r="O262" s="5" t="n">
-        <v>0.062971</v>
+        <v>0.0169</v>
       </c>
       <c r="P262" s="5" t="n">
-        <v>0.072098</v>
+        <v>0.020434</v>
       </c>
       <c r="Q262" s="5" t="n">
-        <v>0.044491</v>
+        <v>0.02076</v>
       </c>
       <c r="R262" s="5" t="n">
-        <v>0.15065</v>
+        <v>0.020999</v>
       </c>
       <c r="S262" s="5" t="n">
-        <v>0.136178</v>
+        <v>0.021055</v>
       </c>
     </row>
     <row r="263">
@@ -31117,14 +31145,10 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Rent</t>
-        </is>
-      </c>
-      <c r="D263" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Legal, audit and accounting</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr"/>
       <c r="E263" t="inlineStr">
         <is>
           <t>-</t>
@@ -31135,62 +31159,44 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G263" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H263" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G263" s="5" t="n">
+        <v>0.03307</v>
+      </c>
+      <c r="H263" s="5" t="n">
+        <v>0.047113</v>
       </c>
       <c r="I263" s="5" t="n">
-        <v>0.06347999999999999</v>
+        <v>0.046795</v>
       </c>
       <c r="J263" s="5" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="K263" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L263" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M263" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N263" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O263" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P263" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q263" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.063184</v>
+      </c>
+      <c r="K263" s="5" t="n">
+        <v>0.030545</v>
+      </c>
+      <c r="L263" s="5" t="n">
+        <v>0.027115</v>
+      </c>
+      <c r="M263" s="5" t="n">
+        <v>0.029378</v>
+      </c>
+      <c r="N263" s="5" t="n">
+        <v>0.02923</v>
+      </c>
+      <c r="O263" s="5" t="n">
+        <v>0.264219</v>
+      </c>
+      <c r="P263" s="5" t="n">
+        <v>0.065058</v>
+      </c>
+      <c r="Q263" s="5" t="n">
+        <v>0.152942</v>
       </c>
       <c r="R263" s="5" t="n">
-        <v>0.036914</v>
+        <v>0.101264</v>
       </c>
       <c r="S263" s="5" t="n">
-        <v>0.054887</v>
+        <v>0.107922</v>
       </c>
     </row>
     <row r="264">
@@ -31206,10 +31212,14 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Share-based compensation (Notes 10, 12c)</t>
-        </is>
-      </c>
-      <c r="D264" t="inlineStr"/>
+          <t>Consulting fees (Note 10)</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E264" t="inlineStr">
         <is>
           <t>-</t>
@@ -31276,10 +31286,10 @@
         </is>
       </c>
       <c r="R264" s="5" t="n">
-        <v>0.434489</v>
+        <v>0.2176</v>
       </c>
       <c r="S264" s="5" t="n">
-        <v>0.313189</v>
+        <v>0.08450000000000001</v>
       </c>
     </row>
     <row r="265">
@@ -31295,7 +31305,7 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Travel</t>
+          <t>Office and miscellaneous</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
@@ -31313,58 +31323,44 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G265" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H265" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G265" s="5" t="n">
+        <v>0.037709</v>
+      </c>
+      <c r="H265" s="5" t="n">
+        <v>0.043633</v>
       </c>
       <c r="I265" s="5" t="n">
-        <v>0.021795</v>
+        <v>0.043192</v>
       </c>
       <c r="J265" s="5" t="n">
-        <v>0.006873</v>
+        <v>0.037462</v>
       </c>
       <c r="K265" s="5" t="n">
-        <v>0.002639</v>
-      </c>
-      <c r="L265" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M265" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N265" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O265" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P265" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.042719</v>
+      </c>
+      <c r="L265" s="5" t="n">
+        <v>0.033811</v>
+      </c>
+      <c r="M265" s="5" t="n">
+        <v>0.005157</v>
+      </c>
+      <c r="N265" s="5" t="n">
+        <v>0.00268</v>
+      </c>
+      <c r="O265" s="5" t="n">
+        <v>0.028774</v>
+      </c>
+      <c r="P265" s="5" t="n">
+        <v>0.030904</v>
       </c>
       <c r="Q265" s="5" t="n">
-        <v>0.000312</v>
+        <v>0.045867</v>
       </c>
       <c r="R265" s="5" t="n">
-        <v>0.034673</v>
+        <v>0.018525</v>
       </c>
       <c r="S265" s="5" t="n">
-        <v>0.039036</v>
+        <v>0.07324700000000001</v>
       </c>
     </row>
     <row r="266">
@@ -31380,10 +31376,14 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Wages and benefits (Note 10)</t>
-        </is>
-      </c>
-      <c r="D266" t="inlineStr"/>
+          <t>Regulatory and transfer agent fees</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E266" t="inlineStr">
         <is>
           <t>-</t>
@@ -31394,66 +31394,44 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G266" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H266" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I266" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J266" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K266" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L266" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M266" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N266" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O266" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P266" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q266" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G266" s="5" t="n">
+        <v>0.028252</v>
+      </c>
+      <c r="H266" s="5" t="n">
+        <v>0.023726</v>
+      </c>
+      <c r="I266" s="5" t="n">
+        <v>0.038921</v>
+      </c>
+      <c r="J266" s="5" t="n">
+        <v>0.018067</v>
+      </c>
+      <c r="K266" s="5" t="n">
+        <v>0.022613</v>
+      </c>
+      <c r="L266" s="5" t="n">
+        <v>0.012261</v>
+      </c>
+      <c r="M266" s="5" t="n">
+        <v>0.026781</v>
+      </c>
+      <c r="N266" s="5" t="n">
+        <v>0.017254</v>
+      </c>
+      <c r="O266" s="5" t="n">
+        <v>0.062971</v>
+      </c>
+      <c r="P266" s="5" t="n">
+        <v>0.072098</v>
+      </c>
+      <c r="Q266" s="5" t="n">
+        <v>0.044491</v>
       </c>
       <c r="R266" s="5" t="n">
-        <v>0.380419</v>
+        <v>0.15065</v>
       </c>
       <c r="S266" s="5" t="n">
-        <v>0.412174</v>
+        <v>0.136178</v>
       </c>
     </row>
     <row r="267">
@@ -31469,10 +31447,14 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Exploration expenditures (Note 7)</t>
-        </is>
-      </c>
-      <c r="D267" t="inlineStr"/>
+          <t>Rent</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E267" t="inlineStr">
         <is>
           <t>-</t>
@@ -31483,52 +31465,58 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G267" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H267" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I267" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J267" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K267" s="5" t="n">
-        <v>0.284927</v>
-      </c>
-      <c r="L267" s="5" t="n">
-        <v>0.074855</v>
-      </c>
-      <c r="M267" s="5" t="n">
-        <v>0.023486</v>
-      </c>
-      <c r="N267" s="5" t="n">
-        <v>0.017107</v>
-      </c>
-      <c r="O267" s="5" t="n">
-        <v>3.138754</v>
-      </c>
-      <c r="P267" s="5" t="n">
-        <v>2.646563</v>
-      </c>
-      <c r="Q267" s="5" t="n">
-        <v>0.094467</v>
+      <c r="G267" s="5" t="n">
+        <v>0.11512</v>
+      </c>
+      <c r="H267" s="5" t="n">
+        <v>0.083132</v>
+      </c>
+      <c r="I267" s="5" t="n">
+        <v>0.06347999999999999</v>
+      </c>
+      <c r="J267" s="5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="K267" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L267" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M267" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N267" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O267" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P267" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q267" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="R267" s="5" t="n">
-        <v>1.601869</v>
+        <v>0.036914</v>
       </c>
       <c r="S267" s="5" t="n">
-        <v>4.953378</v>
+        <v>0.054887</v>
       </c>
     </row>
     <row r="268">
@@ -31544,14 +31532,10 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Expenses total</t>
-        </is>
-      </c>
-      <c r="D268" t="inlineStr">
-        <is>
-          <t>OperatingExpense</t>
-        </is>
-      </c>
+          <t>Share-based compensation (Notes 10, 12c)</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr"/>
       <c r="E268" t="inlineStr">
         <is>
           <t>-</t>
@@ -31572,38 +31556,56 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I268" s="5" t="n">
-        <v>1.51331</v>
-      </c>
-      <c r="J268" s="5" t="n">
-        <v>0.965521</v>
-      </c>
-      <c r="K268" s="5" t="n">
-        <v>0.67561</v>
-      </c>
-      <c r="L268" s="5" t="n">
-        <v>0.313649</v>
-      </c>
-      <c r="M268" s="5" t="n">
-        <v>0.201399</v>
-      </c>
-      <c r="N268" s="5" t="n">
-        <v>0.161226</v>
-      </c>
-      <c r="O268" s="5" t="n">
-        <v>4.799583</v>
-      </c>
-      <c r="P268" s="5" t="n">
-        <v>3.747613</v>
-      </c>
-      <c r="Q268" s="5" t="n">
-        <v>1.023091</v>
+      <c r="I268" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J268" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K268" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L268" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M268" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N268" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O268" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P268" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q268" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="R268" s="5" t="n">
-        <v>3.235258</v>
+        <v>0.434489</v>
       </c>
       <c r="S268" s="5" t="n">
-        <v>6.519039</v>
+        <v>0.313189</v>
       </c>
     </row>
     <row r="269">
@@ -31619,10 +31621,14 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Flow-through premium (Note 5)</t>
-        </is>
-      </c>
-      <c r="D269" t="inlineStr"/>
+          <t>Travel</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E269" t="inlineStr">
         <is>
           <t>-</t>
@@ -31633,30 +31639,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G269" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H269" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I269" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J269" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K269" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G269" s="5" t="n">
+        <v>0.008534999999999999</v>
+      </c>
+      <c r="H269" s="5" t="n">
+        <v>0.004879</v>
+      </c>
+      <c r="I269" s="5" t="n">
+        <v>0.021795</v>
+      </c>
+      <c r="J269" s="5" t="n">
+        <v>0.006873</v>
+      </c>
+      <c r="K269" s="5" t="n">
+        <v>0.002639</v>
       </c>
       <c r="L269" t="inlineStr">
         <is>
@@ -31683,16 +31679,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Q269" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="Q269" s="5" t="n">
+        <v>0.000312</v>
       </c>
       <c r="R269" s="5" t="n">
-        <v>0.016363</v>
+        <v>0.034673</v>
       </c>
       <c r="S269" s="5" t="n">
-        <v>0.69259</v>
+        <v>0.039036</v>
       </c>
     </row>
     <row r="270">
@@ -31708,7 +31702,7 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Gain on sale of mineral property (Note 7)</t>
+          <t>Wages and benefits (Note 10)</t>
         </is>
       </c>
       <c r="D270" t="inlineStr"/>
@@ -31757,8 +31751,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N270" s="5" t="n">
-        <v>0.01</v>
+      <c r="N270" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O270" t="inlineStr">
         <is>
@@ -31776,12 +31772,10 @@
         </is>
       </c>
       <c r="R270" s="5" t="n">
-        <v>1.07735</v>
-      </c>
-      <c r="S270" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.380419</v>
+      </c>
+      <c r="S270" s="5" t="n">
+        <v>0.412174</v>
       </c>
     </row>
     <row r="271">
@@ -31797,7 +31791,7 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Write-down of mineral properties (Note 7)</t>
+          <t>Exploration expenditures (Note 7)</t>
         </is>
       </c>
       <c r="D271" t="inlineStr"/>
@@ -31832,41 +31826,31 @@
         </is>
       </c>
       <c r="K271" s="5" t="n">
-        <v>-0.35176</v>
+        <v>0.284927</v>
       </c>
       <c r="L271" s="5" t="n">
-        <v>-0.352465</v>
+        <v>0.074855</v>
       </c>
       <c r="M271" s="5" t="n">
-        <v>-0.0525</v>
-      </c>
-      <c r="N271" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O271" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P271" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q271" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.023486</v>
+      </c>
+      <c r="N271" s="5" t="n">
+        <v>0.017107</v>
+      </c>
+      <c r="O271" s="5" t="n">
+        <v>3.138754</v>
+      </c>
+      <c r="P271" s="5" t="n">
+        <v>2.646563</v>
+      </c>
+      <c r="Q271" s="5" t="n">
+        <v>0.094467</v>
       </c>
       <c r="R271" s="5" t="n">
-        <v>-0.6011570000000001</v>
-      </c>
-      <c r="S271" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1.601869</v>
+      </c>
+      <c r="S271" s="5" t="n">
+        <v>4.953378</v>
       </c>
     </row>
     <row r="272">
@@ -31882,10 +31866,14 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Unrealized gain (loss) on marketable securities (Note 4)</t>
-        </is>
-      </c>
-      <c r="D272" t="inlineStr"/>
+          <t>Expenses total</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
       <c r="E272" t="inlineStr">
         <is>
           <t>-</t>
@@ -31896,64 +31884,44 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G272" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H272" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I272" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J272" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K272" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L272" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M272" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N272" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O272" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P272" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G272" s="5" t="n">
+        <v>0.877555</v>
+      </c>
+      <c r="H272" s="5" t="n">
+        <v>0.856069</v>
+      </c>
+      <c r="I272" s="5" t="n">
+        <v>1.51331</v>
+      </c>
+      <c r="J272" s="5" t="n">
+        <v>0.965521</v>
+      </c>
+      <c r="K272" s="5" t="n">
+        <v>0.67561</v>
+      </c>
+      <c r="L272" s="5" t="n">
+        <v>0.313649</v>
+      </c>
+      <c r="M272" s="5" t="n">
+        <v>0.201399</v>
+      </c>
+      <c r="N272" s="5" t="n">
+        <v>0.161226</v>
+      </c>
+      <c r="O272" s="5" t="n">
+        <v>4.799583</v>
+      </c>
+      <c r="P272" s="5" t="n">
+        <v>3.747613</v>
       </c>
       <c r="Q272" s="5" t="n">
-        <v>5.2e-05</v>
+        <v>1.023091</v>
       </c>
       <c r="R272" s="5" t="n">
-        <v>-0.612428</v>
+        <v>3.235258</v>
       </c>
       <c r="S272" s="5" t="n">
-        <v>0.075309</v>
+        <v>6.519039</v>
       </c>
     </row>
     <row r="273">
@@ -31969,7 +31937,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Realized gain on marketable securities (Note</t>
+          <t>Flow-through premium (Note 5)</t>
         </is>
       </c>
       <c r="D273" t="inlineStr"/>
@@ -32039,10 +32007,10 @@
         </is>
       </c>
       <c r="R273" s="5" t="n">
-        <v>0.26875</v>
+        <v>0.016363</v>
       </c>
       <c r="S273" s="5" t="n">
-        <v>4e-06</v>
+        <v>0.69259</v>
       </c>
     </row>
     <row r="274">
@@ -32058,7 +32026,7 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Miscellaneous revenue (Note 18)</t>
+          <t>Gain on sale of mineral property (Note 7)</t>
         </is>
       </c>
       <c r="D274" t="inlineStr"/>
@@ -32107,10 +32075,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N274" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N274" s="5" t="n">
+        <v>0.01</v>
       </c>
       <c r="O274" t="inlineStr">
         <is>
@@ -32128,10 +32094,12 @@
         </is>
       </c>
       <c r="R274" s="5" t="n">
-        <v>0.08076</v>
-      </c>
-      <c r="S274" s="5" t="n">
-        <v>0.354139</v>
+        <v>1.07735</v>
+      </c>
+      <c r="S274" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="275">
@@ -32147,14 +32115,10 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Interest income</t>
-        </is>
-      </c>
-      <c r="D275" t="inlineStr">
-        <is>
-          <t>InterestIncomeNonOperating</t>
-        </is>
-      </c>
+          <t>Write-down of mineral properties (Note 7)</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr"/>
       <c r="E275" t="inlineStr">
         <is>
           <t>-</t>
@@ -32180,20 +32144,24 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J275" s="5" t="n">
-        <v>0.001344</v>
+      <c r="J275" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K275" s="5" t="n">
-        <v>0.000166</v>
+        <v>-0.35176</v>
       </c>
       <c r="L275" s="5" t="n">
-        <v>0.000279</v>
+        <v>-0.352465</v>
       </c>
       <c r="M275" s="5" t="n">
-        <v>6.2e-05</v>
-      </c>
-      <c r="N275" s="5" t="n">
-        <v>5.8e-05</v>
+        <v>-0.0525</v>
+      </c>
+      <c r="N275" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O275" t="inlineStr">
         <is>
@@ -32205,14 +32173,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Q275" s="5" t="n">
-        <v>0.009669000000000001</v>
+      <c r="Q275" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="R275" s="5" t="n">
-        <v>0.035358</v>
-      </c>
-      <c r="S275" s="5" t="n">
-        <v>0.052945</v>
+        <v>-0.6011570000000001</v>
+      </c>
+      <c r="S275" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="276">
@@ -32228,14 +32200,10 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Loss and comprehensive loss for the year $</t>
-        </is>
-      </c>
-      <c r="D276" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Unrealized gain (loss) on marketable securities (Note 4)</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr"/>
       <c r="E276" t="inlineStr">
         <is>
           <t>-</t>
@@ -32256,17 +32224,25 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I276" s="5" t="n">
-        <v>-1.656563</v>
-      </c>
-      <c r="J276" s="5" t="n">
-        <v>-0.954315</v>
-      </c>
-      <c r="K276" s="5" t="n">
-        <v>-0.963432</v>
-      </c>
-      <c r="L276" s="5" t="n">
-        <v>-0.6026319999999999</v>
+      <c r="I276" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J276" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K276" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L276" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M276" t="inlineStr">
         <is>
@@ -32289,13 +32265,13 @@
         </is>
       </c>
       <c r="Q276" s="5" t="n">
-        <v>-1.01337</v>
+        <v>5.2e-05</v>
       </c>
       <c r="R276" s="5" t="n">
-        <v>-3.239012</v>
+        <v>-0.612428</v>
       </c>
       <c r="S276" s="5" t="n">
-        <v>-5.075306</v>
+        <v>0.075309</v>
       </c>
     </row>
     <row r="277">
@@ -32311,14 +32287,10 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Basic and diluted loss per common share $</t>
-        </is>
-      </c>
-      <c r="D277" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
+          <t>Realized gain on marketable securities (Note</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr"/>
       <c r="E277" t="inlineStr">
         <is>
           <t>-</t>
@@ -32339,17 +32311,25 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I277" s="5" t="n">
-        <v>-3e-08</v>
-      </c>
-      <c r="J277" s="5" t="n">
-        <v>-1e-08</v>
-      </c>
-      <c r="K277" s="5" t="n">
-        <v>-1e-08</v>
-      </c>
-      <c r="L277" s="5" t="n">
-        <v>-1e-08</v>
+      <c r="I277" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J277" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K277" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L277" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M277" t="inlineStr">
         <is>
@@ -32361,20 +32341,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O277" s="5" t="n">
-        <v>-8e-08</v>
-      </c>
-      <c r="P277" s="5" t="n">
-        <v>-5e-08</v>
-      </c>
-      <c r="Q277" s="5" t="n">
-        <v>-1e-08</v>
+      <c r="O277" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P277" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q277" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="R277" s="5" t="n">
-        <v>-2e-08</v>
+        <v>0.26875</v>
       </c>
       <c r="S277" s="5" t="n">
-        <v>-1e-08</v>
+        <v>4e-06</v>
       </c>
     </row>
     <row r="278">
@@ -32385,12 +32371,12 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Weighted average number</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding – basic and diluted</t>
+          <t>Miscellaneous revenue (Note 18)</t>
         </is>
       </c>
       <c r="D278" t="inlineStr"/>
@@ -32429,29 +32415,41 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L278" s="5" t="n">
-        <v>84.442786</v>
-      </c>
-      <c r="M278" s="5" t="n">
-        <v>85.81438900000001</v>
-      </c>
-      <c r="N278" s="5" t="n">
-        <v>89.86487</v>
-      </c>
-      <c r="O278" s="5" t="n">
-        <v>60.608923</v>
-      </c>
-      <c r="P278" s="5" t="n">
-        <v>76.979799</v>
-      </c>
-      <c r="Q278" s="5" t="n">
-        <v>94.44505700000001</v>
+      <c r="L278" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M278" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N278" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O278" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P278" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q278" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="R278" s="5" t="n">
-        <v>210.640916</v>
+        <v>0.08076</v>
       </c>
       <c r="S278" s="5" t="n">
-        <v>347.580659</v>
+        <v>0.354139</v>
       </c>
     </row>
     <row r="279">
@@ -32467,12 +32465,12 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Consulting fees (Note 9)</t>
+          <t>Interest income</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
@@ -32485,62 +32483,50 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G279" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H279" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G279" s="5" t="n">
+        <v>0.013911</v>
+      </c>
+      <c r="H279" s="5" t="n">
+        <v>0.004406</v>
       </c>
       <c r="I279" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J279" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K279" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L279" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M279" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N279" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O279" s="5" t="n">
-        <v>0.10565</v>
-      </c>
-      <c r="P279" s="5" t="n">
-        <v>0.08400000000000001</v>
+      <c r="J279" s="5" t="n">
+        <v>0.001344</v>
+      </c>
+      <c r="K279" s="5" t="n">
+        <v>0.000166</v>
+      </c>
+      <c r="L279" s="5" t="n">
+        <v>0.000279</v>
+      </c>
+      <c r="M279" s="5" t="n">
+        <v>6.2e-05</v>
+      </c>
+      <c r="N279" s="5" t="n">
+        <v>5.8e-05</v>
+      </c>
+      <c r="O279" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P279" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="Q279" s="5" t="n">
-        <v>0.157922</v>
+        <v>0.009669000000000001</v>
       </c>
       <c r="R279" s="5" t="n">
-        <v>0.2176</v>
-      </c>
-      <c r="S279" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.035358</v>
+      </c>
+      <c r="S279" s="5" t="n">
+        <v>0.052945</v>
       </c>
     </row>
     <row r="280">
@@ -32556,12 +32542,12 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Rent (Note 9)</t>
+          <t>Loss and comprehensive loss for the year $</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>NetIncome</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
@@ -32574,54 +32560,52 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G280" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H280" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I280" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J280" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G280" s="5" t="n">
+        <v>-2.378742</v>
+      </c>
+      <c r="H280" s="5" t="n">
+        <v>-8.677626999999999</v>
+      </c>
+      <c r="I280" s="5" t="n">
+        <v>-1.656563</v>
+      </c>
+      <c r="J280" s="5" t="n">
+        <v>-0.954315</v>
       </c>
       <c r="K280" s="5" t="n">
-        <v>0.042</v>
+        <v>-0.963432</v>
       </c>
       <c r="L280" s="5" t="n">
-        <v>0.042</v>
-      </c>
-      <c r="M280" s="5" t="n">
-        <v>0.018</v>
-      </c>
-      <c r="N280" s="5" t="n">
-        <v>0.018</v>
-      </c>
-      <c r="O280" s="5" t="n">
-        <v>0.01522</v>
-      </c>
-      <c r="P280" s="5" t="n">
-        <v>0.01608</v>
+        <v>-0.6026319999999999</v>
+      </c>
+      <c r="M280" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N280" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O280" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P280" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="Q280" s="5" t="n">
-        <v>0.01608</v>
+        <v>-1.01337</v>
       </c>
       <c r="R280" s="5" t="n">
-        <v>0.036914</v>
-      </c>
-      <c r="S280" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-3.239012</v>
+      </c>
+      <c r="S280" s="5" t="n">
+        <v>-5.075306</v>
       </c>
     </row>
     <row r="281">
@@ -32637,10 +32621,14 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Share-based compensation (Notes 9, 10c)</t>
-        </is>
-      </c>
-      <c r="D281" t="inlineStr"/>
+          <t>Basic and diluted loss per common share $</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E281" t="inlineStr">
         <is>
           <t>-</t>
@@ -32651,35 +32639,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G281" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H281" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I281" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J281" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K281" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L281" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G281" s="5" t="n">
+        <v>-5e-08</v>
+      </c>
+      <c r="H281" s="5" t="n">
+        <v>-1.7e-07</v>
+      </c>
+      <c r="I281" s="5" t="n">
+        <v>-3e-08</v>
+      </c>
+      <c r="J281" s="5" t="n">
+        <v>-1e-08</v>
+      </c>
+      <c r="K281" s="5" t="n">
+        <v>-1e-08</v>
+      </c>
+      <c r="L281" s="5" t="n">
+        <v>-1e-08</v>
       </c>
       <c r="M281" t="inlineStr">
         <is>
@@ -32691,26 +32667,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O281" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P281" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O281" s="5" t="n">
+        <v>-8e-08</v>
+      </c>
+      <c r="P281" s="5" t="n">
+        <v>-5e-08</v>
       </c>
       <c r="Q281" s="5" t="n">
-        <v>0.261432</v>
+        <v>-1e-08</v>
       </c>
       <c r="R281" s="5" t="n">
-        <v>0.434489</v>
-      </c>
-      <c r="S281" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-2e-08</v>
+      </c>
+      <c r="S281" s="5" t="n">
+        <v>-1e-08</v>
       </c>
     </row>
     <row r="282">
@@ -32721,12 +32691,12 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Weighted average number</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Wages and benefits (Note 9)</t>
+          <t>Weighted average number of common shares outstanding – basic and diluted</t>
         </is>
       </c>
       <c r="D282" t="inlineStr"/>
@@ -32765,41 +32735,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L282" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M282" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N282" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O282" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P282" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L282" s="5" t="n">
+        <v>84.442786</v>
+      </c>
+      <c r="M282" s="5" t="n">
+        <v>85.81438900000001</v>
+      </c>
+      <c r="N282" s="5" t="n">
+        <v>89.86487</v>
+      </c>
+      <c r="O282" s="5" t="n">
+        <v>60.608923</v>
+      </c>
+      <c r="P282" s="5" t="n">
+        <v>76.979799</v>
       </c>
       <c r="Q282" s="5" t="n">
-        <v>0.190911</v>
+        <v>94.44505700000001</v>
       </c>
       <c r="R282" s="5" t="n">
-        <v>0.380419</v>
-      </c>
-      <c r="S282" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>210.640916</v>
+      </c>
+      <c r="S282" s="5" t="n">
+        <v>347.580659</v>
       </c>
     </row>
     <row r="283">
@@ -32815,10 +32773,14 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Gain on sale of mineral property (Note 16)</t>
-        </is>
-      </c>
-      <c r="D283" t="inlineStr"/>
+          <t>Consulting fees (Note 9)</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E283" t="inlineStr">
         <is>
           <t>-</t>
@@ -32869,23 +32831,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O283" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P283" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q283" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O283" s="5" t="n">
+        <v>0.10565</v>
+      </c>
+      <c r="P283" s="5" t="n">
+        <v>0.08400000000000001</v>
+      </c>
+      <c r="Q283" s="5" t="n">
+        <v>0.157922</v>
       </c>
       <c r="R283" s="5" t="n">
-        <v>1.07735</v>
+        <v>0.2176</v>
       </c>
       <c r="S283" t="inlineStr">
         <is>
@@ -32906,10 +32862,14 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Miscellaneous revenue</t>
-        </is>
-      </c>
-      <c r="D284" t="inlineStr"/>
+          <t>Rent (Note 9)</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E284" t="inlineStr">
         <is>
           <t>-</t>
@@ -32940,43 +32900,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K284" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L284" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M284" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N284" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O284" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P284" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q284" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K284" s="5" t="n">
+        <v>0.042</v>
+      </c>
+      <c r="L284" s="5" t="n">
+        <v>0.042</v>
+      </c>
+      <c r="M284" s="5" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="N284" s="5" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="O284" s="5" t="n">
+        <v>0.01522</v>
+      </c>
+      <c r="P284" s="5" t="n">
+        <v>0.01608</v>
+      </c>
+      <c r="Q284" s="5" t="n">
+        <v>0.01608</v>
       </c>
       <c r="R284" s="5" t="n">
-        <v>0.08076</v>
+        <v>0.036914</v>
       </c>
       <c r="S284" t="inlineStr">
         <is>
@@ -32997,7 +32943,7 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Share-based compensation (Note 10c)</t>
+          <t>Share-based compensation (Notes 9, 10c)</t>
         </is>
       </c>
       <c r="D285" t="inlineStr"/>
@@ -33051,19 +32997,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O285" s="5" t="n">
-        <v>0.991209</v>
-      </c>
-      <c r="P285" s="5" t="n">
-        <v>0.52683</v>
+      <c r="O285" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P285" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="Q285" s="5" t="n">
         <v>0.261432</v>
       </c>
-      <c r="R285" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="R285" s="5" t="n">
+        <v>0.434489</v>
       </c>
       <c r="S285" t="inlineStr">
         <is>
@@ -33084,7 +33032,7 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Wages and benefits</t>
+          <t>Wages and benefits (Note 9)</t>
         </is>
       </c>
       <c r="D286" t="inlineStr"/>
@@ -33108,37 +33056,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I286" s="5" t="n">
-        <v>0.09358900000000001</v>
-      </c>
-      <c r="J286" s="5" t="n">
-        <v>0.10793</v>
-      </c>
-      <c r="K286" s="5" t="n">
-        <v>0.040205</v>
-      </c>
-      <c r="L286" s="5" t="n">
-        <v>0.007922999999999999</v>
-      </c>
-      <c r="M286" s="5" t="n">
-        <v>0.011588</v>
-      </c>
-      <c r="N286" s="5" t="n">
-        <v>0.009181</v>
-      </c>
-      <c r="O286" s="5" t="n">
-        <v>0.126671</v>
-      </c>
-      <c r="P286" s="5" t="n">
-        <v>0.23236</v>
+      <c r="I286" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J286" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K286" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L286" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M286" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N286" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O286" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P286" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="Q286" s="5" t="n">
         <v>0.190911</v>
       </c>
-      <c r="R286" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="R286" s="5" t="n">
+        <v>0.380419</v>
       </c>
       <c r="S286" t="inlineStr">
         <is>
@@ -33159,7 +33121,7 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Flow-through premium (Note 10)</t>
+          <t>Gain on sale of mineral property (Note 16)</t>
         </is>
       </c>
       <c r="D287" t="inlineStr"/>
@@ -33218,18 +33180,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P287" s="5" t="n">
-        <v>0.109757</v>
+      <c r="P287" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="Q287" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="R287" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="R287" s="5" t="n">
+        <v>1.07735</v>
       </c>
       <c r="S287" t="inlineStr">
         <is>
@@ -33250,7 +33212,7 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Unrealized gain (loss) on marketable securities</t>
+          <t>Miscellaneous revenue</t>
         </is>
       </c>
       <c r="D288" t="inlineStr"/>
@@ -33309,16 +33271,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P288" s="5" t="n">
-        <v>-0.000828</v>
-      </c>
-      <c r="Q288" s="5" t="n">
-        <v>5.2e-05</v>
-      </c>
-      <c r="R288" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P288" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q288" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R288" s="5" t="n">
+        <v>0.08076</v>
       </c>
       <c r="S288" t="inlineStr">
         <is>
@@ -33339,14 +33303,10 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss for the year $</t>
-        </is>
-      </c>
-      <c r="D289" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Share-based compensation (Note 10c)</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr"/>
       <c r="E289" t="inlineStr">
         <is>
           <t>-</t>
@@ -33398,13 +33358,13 @@
         </is>
       </c>
       <c r="O289" s="5" t="n">
-        <v>-4.798703</v>
+        <v>0.991209</v>
       </c>
       <c r="P289" s="5" t="n">
-        <v>-3.638684</v>
+        <v>0.52683</v>
       </c>
       <c r="Q289" s="5" t="n">
-        <v>-1.01337</v>
+        <v>0.261432</v>
       </c>
       <c r="R289" t="inlineStr">
         <is>
@@ -33430,7 +33390,7 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Flow-through premium</t>
+          <t>Wages and benefits</t>
         </is>
       </c>
       <c r="D290" t="inlineStr"/>
@@ -33444,56 +33404,38 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G290" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H290" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I290" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J290" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K290" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L290" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M290" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N290" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G290" s="5" t="n">
+        <v>0.104102</v>
+      </c>
+      <c r="H290" s="5" t="n">
+        <v>0.09124500000000001</v>
+      </c>
+      <c r="I290" s="5" t="n">
+        <v>0.09358900000000001</v>
+      </c>
+      <c r="J290" s="5" t="n">
+        <v>0.10793</v>
+      </c>
+      <c r="K290" s="5" t="n">
+        <v>0.040205</v>
+      </c>
+      <c r="L290" s="5" t="n">
+        <v>0.007922999999999999</v>
+      </c>
+      <c r="M290" s="5" t="n">
+        <v>0.011588</v>
+      </c>
+      <c r="N290" s="5" t="n">
+        <v>0.009181</v>
       </c>
       <c r="O290" s="5" t="n">
-        <v>0.001018</v>
+        <v>0.126671</v>
       </c>
       <c r="P290" s="5" t="n">
-        <v>0.109757</v>
-      </c>
-      <c r="Q290" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.23236</v>
+      </c>
+      <c r="Q290" s="5" t="n">
+        <v>0.190911</v>
       </c>
       <c r="R290" t="inlineStr">
         <is>
@@ -33519,7 +33461,7 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Unrealized loss on marketable securities</t>
+          <t>Flow-through premium (Note 10)</t>
         </is>
       </c>
       <c r="D291" t="inlineStr"/>
@@ -33573,11 +33515,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O291" s="5" t="n">
-        <v>-0.000138</v>
+      <c r="O291" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="P291" s="5" t="n">
-        <v>-0.000828</v>
+        <v>0.109757</v>
       </c>
       <c r="Q291" t="inlineStr">
         <is>
@@ -33608,7 +33552,7 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Interest (Note 9)</t>
+          <t>Unrealized gain (loss) on marketable securities</t>
         </is>
       </c>
       <c r="D292" t="inlineStr"/>
@@ -33657,23 +33601,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N292" s="5" t="n">
-        <v>0.012388</v>
+      <c r="N292" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O292" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="P292" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q292" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P292" s="5" t="n">
+        <v>-0.000828</v>
+      </c>
+      <c r="Q292" s="5" t="n">
+        <v>5.2e-05</v>
       </c>
       <c r="R292" t="inlineStr">
         <is>
@@ -33699,12 +33641,12 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Management fees (Note 9)</t>
+          <t>Net loss and comprehensive loss for the year $</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>NetIncome</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
@@ -33737,32 +33679,34 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K293" s="5" t="n">
-        <v>0.11825</v>
-      </c>
-      <c r="L293" s="5" t="n">
-        <v>0.11175</v>
-      </c>
-      <c r="M293" s="5" t="n">
-        <v>0.082687</v>
-      </c>
-      <c r="N293" s="5" t="n">
-        <v>0.044147</v>
-      </c>
-      <c r="O293" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P293" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q293" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K293" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L293" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M293" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N293" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O293" s="5" t="n">
+        <v>-4.798703</v>
+      </c>
+      <c r="P293" s="5" t="n">
+        <v>-3.638684</v>
+      </c>
+      <c r="Q293" s="5" t="n">
+        <v>-1.01337</v>
       </c>
       <c r="R293" t="inlineStr">
         <is>
@@ -33788,7 +33732,7 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Unrealized (loss) gain on marketable securities</t>
+          <t>Flow-through premium</t>
         </is>
       </c>
       <c r="D294" t="inlineStr"/>
@@ -33832,21 +33776,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M294" s="5" t="n">
-        <v>0.0005</v>
-      </c>
-      <c r="N294" s="5" t="n">
-        <v>-0.001208</v>
-      </c>
-      <c r="O294" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P294" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M294" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N294" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O294" s="5" t="n">
+        <v>0.001018</v>
+      </c>
+      <c r="P294" s="5" t="n">
+        <v>0.109757</v>
       </c>
       <c r="Q294" t="inlineStr">
         <is>
@@ -33877,7 +33821,7 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Realized gain on marketable securities</t>
+          <t>Unrealized loss on marketable securities</t>
         </is>
       </c>
       <c r="D295" t="inlineStr"/>
@@ -33916,26 +33860,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L295" s="5" t="n">
-        <v>0.003275</v>
-      </c>
-      <c r="M295" s="5" t="n">
-        <v>0.00085</v>
+      <c r="L295" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M295" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N295" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="O295" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P295" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O295" s="5" t="n">
+        <v>-0.000138</v>
+      </c>
+      <c r="P295" s="5" t="n">
+        <v>-0.000828</v>
       </c>
       <c r="Q295" t="inlineStr">
         <is>
@@ -33966,7 +33910,7 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Write-down of mineral properties (Note 7a)</t>
+          <t>Interest (Note 9)</t>
         </is>
       </c>
       <c r="D296" t="inlineStr"/>
@@ -34010,13 +33954,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M296" s="5" t="n">
-        <v>-0.0525</v>
-      </c>
-      <c r="N296" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M296" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N296" s="5" t="n">
+        <v>0.012388</v>
       </c>
       <c r="O296" t="inlineStr">
         <is>
@@ -34057,10 +34001,14 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Write-off of accounts payable (Note 10)</t>
-        </is>
-      </c>
-      <c r="D297" t="inlineStr"/>
+          <t>Management fees (Note 9)</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E297" t="inlineStr">
         <is>
           <t>-</t>
@@ -34091,23 +34039,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K297" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L297" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K297" s="5" t="n">
+        <v>0.11825</v>
+      </c>
+      <c r="L297" s="5" t="n">
+        <v>0.11175</v>
       </c>
       <c r="M297" s="5" t="n">
-        <v>0.483559</v>
-      </c>
-      <c r="N297" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.082687</v>
+      </c>
+      <c r="N297" s="5" t="n">
+        <v>0.044147</v>
       </c>
       <c r="O297" t="inlineStr">
         <is>
@@ -34148,14 +34090,10 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Net earnings (loss) and comprehensive earnings (loss) for the year $</t>
-        </is>
-      </c>
-      <c r="D298" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Unrealized (loss) gain on marketable securities</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr"/>
       <c r="E298" t="inlineStr">
         <is>
           <t>-</t>
@@ -34191,14 +34129,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L298" s="5" t="n">
-        <v>-0.6026319999999999</v>
+      <c r="L298" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M298" s="5" t="n">
-        <v>0.231072</v>
+        <v>0.0005</v>
       </c>
       <c r="N298" s="5" t="n">
-        <v>-0.152376</v>
+        <v>-0.001208</v>
       </c>
       <c r="O298" t="inlineStr">
         <is>
@@ -34239,7 +34179,7 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Basic and diluted earning (loss) per common share $</t>
+          <t>Realized gain on marketable securities</t>
         </is>
       </c>
       <c r="D299" t="inlineStr"/>
@@ -34279,13 +34219,15 @@
         </is>
       </c>
       <c r="L299" s="5" t="n">
-        <v>-1e-08</v>
+        <v>0.003275</v>
       </c>
       <c r="M299" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N299" s="5" t="n">
-        <v>0</v>
+        <v>0.00085</v>
+      </c>
+      <c r="N299" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O299" t="inlineStr">
         <is>
@@ -34326,7 +34268,7 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Unrealized gain on marketable securities</t>
+          <t>Write-down of mineral properties (Note 7a)</t>
         </is>
       </c>
       <c r="D300" t="inlineStr"/>
@@ -34365,11 +34307,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L300" s="5" t="n">
-        <v>0.003508</v>
+      <c r="L300" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M300" s="5" t="n">
-        <v>0.0005</v>
+        <v>-0.0525</v>
       </c>
       <c r="N300" t="inlineStr">
         <is>
@@ -34415,7 +34359,7 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>Write-off of accounts payable (Note 10b)</t>
+          <t>Write-off of accounts payable (Note 10)</t>
         </is>
       </c>
       <c r="D301" t="inlineStr"/>
@@ -34454,8 +34398,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L301" s="5" t="n">
-        <v>0.05642</v>
+      <c r="L301" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M301" s="5" t="n">
         <v>0.483559</v>
@@ -34504,10 +34450,14 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Share-based compensation (Note 10e)</t>
-        </is>
-      </c>
-      <c r="D302" t="inlineStr"/>
+          <t>Net earnings (loss) and comprehensive earnings (loss) for the year $</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E302" t="inlineStr">
         <is>
           <t>-</t>
@@ -34528,31 +34478,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I302" s="5" t="n">
-        <v>0.04901</v>
+      <c r="I302" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J302" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K302" s="5" t="n">
-        <v>0.05436</v>
-      </c>
-      <c r="L302" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M302" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N302" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K302" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L302" s="5" t="n">
+        <v>-0.6026319999999999</v>
+      </c>
+      <c r="M302" s="5" t="n">
+        <v>0.231072</v>
+      </c>
+      <c r="N302" s="5" t="n">
+        <v>-0.152376</v>
       </c>
       <c r="O302" t="inlineStr">
         <is>
@@ -34593,7 +34541,7 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Unrealized gain on marketable securities (Note 4)</t>
+          <t>Basic and diluted earning (loss) per common share $</t>
         </is>
       </c>
       <c r="D303" t="inlineStr"/>
@@ -34627,21 +34575,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K303" s="5" t="n">
-        <v>0.102075</v>
+      <c r="K303" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L303" s="5" t="n">
-        <v>0.003508</v>
-      </c>
-      <c r="M303" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N303" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-1e-08</v>
+      </c>
+      <c r="M303" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N303" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="O303" t="inlineStr">
         <is>
@@ -34682,7 +34628,7 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Realized (loss)/gain on marketable securities (Note 4)</t>
+          <t>Unrealized gain on marketable securities</t>
         </is>
       </c>
       <c r="D304" t="inlineStr"/>
@@ -34716,16 +34662,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K304" s="5" t="n">
-        <v>-0.053062</v>
+      <c r="K304" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L304" s="5" t="n">
-        <v>0.003275</v>
-      </c>
-      <c r="M304" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.003508</v>
+      </c>
+      <c r="M304" s="5" t="n">
+        <v>0.0005</v>
       </c>
       <c r="N304" t="inlineStr">
         <is>
@@ -34771,7 +34717,7 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>Write-off of accounts payable</t>
+          <t>Write-off of accounts payable (Note 10b)</t>
         </is>
       </c>
       <c r="D305" t="inlineStr"/>
@@ -34813,10 +34759,8 @@
       <c r="L305" s="5" t="n">
         <v>0.05642</v>
       </c>
-      <c r="M305" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M305" s="5" t="n">
+        <v>0.483559</v>
       </c>
       <c r="N305" t="inlineStr">
         <is>
@@ -34862,7 +34806,7 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>Flow through premium (Note 10c)</t>
+          <t>Share-based compensation (Note 10e)</t>
         </is>
       </c>
       <c r="D306" t="inlineStr"/>
@@ -34887,13 +34831,15 @@
         </is>
       </c>
       <c r="I306" s="5" t="n">
-        <v>0.200237</v>
-      </c>
-      <c r="J306" s="5" t="n">
-        <v>0.09926500000000001</v>
+        <v>0.04901</v>
+      </c>
+      <c r="J306" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K306" s="5" t="n">
-        <v>0.014759</v>
+        <v>0.05436</v>
       </c>
       <c r="L306" t="inlineStr">
         <is>
@@ -34944,42 +34890,50 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>Weighted average number</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding</t>
-        </is>
-      </c>
-      <c r="D307" t="inlineStr">
-        <is>
-          <t>SharesOutstanding</t>
-        </is>
-      </c>
-      <c r="E307" s="5" t="n">
-        <v>35.672538</v>
-      </c>
-      <c r="F307" s="5" t="n">
-        <v>36.297687</v>
-      </c>
-      <c r="G307" s="5" t="n">
-        <v>49.411009</v>
-      </c>
-      <c r="H307" s="5" t="n">
-        <v>49.813749</v>
-      </c>
-      <c r="I307" s="5" t="n">
-        <v>60.469815</v>
-      </c>
-      <c r="J307" s="5" t="n">
-        <v>76.239092</v>
+          <t>Unrealized gain on marketable securities (Note 4)</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr"/>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F307" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G307" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H307" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I307" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J307" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K307" s="5" t="n">
-        <v>82.996483</v>
+        <v>0.102075</v>
       </c>
       <c r="L307" s="5" t="n">
-        <v>84.442786</v>
+        <v>0.003508</v>
       </c>
       <c r="M307" t="inlineStr">
         <is>
@@ -35030,7 +34984,7 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>Management fees and corporate services</t>
+          <t>Realized (loss)/gain on marketable securities (Note 4)</t>
         </is>
       </c>
       <c r="D308" t="inlineStr"/>
@@ -35054,21 +35008,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I308" s="5" t="n">
-        <v>0.11045</v>
-      </c>
-      <c r="J308" s="5" t="n">
-        <v>0.1319</v>
-      </c>
-      <c r="K308" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L308" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I308" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J308" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K308" s="5" t="n">
+        <v>-0.053062</v>
+      </c>
+      <c r="L308" s="5" t="n">
+        <v>0.003275</v>
       </c>
       <c r="M308" t="inlineStr">
         <is>
@@ -35119,7 +35073,7 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>Exploration expenditures (Note 8)</t>
+          <t>Write-off of accounts payable</t>
         </is>
       </c>
       <c r="D309" t="inlineStr"/>
@@ -35143,21 +35097,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I309" s="5" t="n">
-        <v>0.894221</v>
-      </c>
-      <c r="J309" s="5" t="n">
-        <v>0.423479</v>
+      <c r="I309" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J309" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K309" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="L309" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L309" s="5" t="n">
+        <v>0.05642</v>
       </c>
       <c r="M309" t="inlineStr">
         <is>
@@ -35208,7 +35164,7 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Unrealized (loss)/gain on marketable securities (Note 4)</t>
+          <t>Flow through premium (Note 10c)</t>
         </is>
       </c>
       <c r="D310" t="inlineStr"/>
@@ -35233,15 +35189,13 @@
         </is>
       </c>
       <c r="I310" s="5" t="n">
-        <v>-0.192781</v>
+        <v>0.200237</v>
       </c>
       <c r="J310" s="5" t="n">
-        <v>-0.008815</v>
-      </c>
-      <c r="K310" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.09926500000000001</v>
+      </c>
+      <c r="K310" s="5" t="n">
+        <v>0.014759</v>
       </c>
       <c r="L310" t="inlineStr">
         <is>
@@ -35292,52 +35246,42 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Weighted average number</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Realized (loss)/gain on marketable securities</t>
-        </is>
-      </c>
-      <c r="D311" t="inlineStr"/>
-      <c r="E311" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F311" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G311" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H311" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Weighted average number of common shares outstanding</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>SharesOutstanding</t>
+        </is>
+      </c>
+      <c r="E311" s="5" t="n">
+        <v>35.672538</v>
+      </c>
+      <c r="F311" s="5" t="n">
+        <v>36.297687</v>
+      </c>
+      <c r="G311" s="5" t="n">
+        <v>49.411009</v>
+      </c>
+      <c r="H311" s="5" t="n">
+        <v>49.813749</v>
       </c>
       <c r="I311" s="5" t="n">
-        <v>-0.280597</v>
-      </c>
-      <c r="J311" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K311" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L311" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>60.469815</v>
+      </c>
+      <c r="J311" s="5" t="n">
+        <v>76.239092</v>
+      </c>
+      <c r="K311" s="5" t="n">
+        <v>82.996483</v>
+      </c>
+      <c r="L311" s="5" t="n">
+        <v>84.442786</v>
       </c>
       <c r="M311" t="inlineStr">
         <is>
@@ -35388,7 +35332,7 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>Gain/(loss) on sale of mineral property (Note 8a)</t>
+          <t>Management fees and corporate services</t>
         </is>
       </c>
       <c r="D312" t="inlineStr"/>
@@ -35402,23 +35346,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G312" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H312" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G312" s="5" t="n">
+        <v>0.01791</v>
+      </c>
+      <c r="H312" s="5" t="n">
+        <v>0.020875</v>
       </c>
       <c r="I312" s="5" t="n">
-        <v>0.129888</v>
-      </c>
-      <c r="J312" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.11045</v>
+      </c>
+      <c r="J312" s="5" t="n">
+        <v>0.1319</v>
       </c>
       <c r="K312" t="inlineStr">
         <is>
@@ -35479,7 +35417,7 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>Write-down of mineral properties (Note 8)</t>
+          <t>Exploration expenditures (Note 8)</t>
         </is>
       </c>
       <c r="D313" t="inlineStr"/>
@@ -35493,23 +35431,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G313" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H313" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I313" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G313" s="5" t="n">
+        <v>0.44555</v>
+      </c>
+      <c r="H313" s="5" t="n">
+        <v>0.375087</v>
+      </c>
+      <c r="I313" s="5" t="n">
+        <v>0.894221</v>
       </c>
       <c r="J313" s="5" t="n">
-        <v>-0.08058800000000001</v>
+        <v>0.423479</v>
       </c>
       <c r="K313" t="inlineStr">
         <is>
@@ -35565,19 +35497,15 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>Depreciation                                                                                                                ‐           28,410</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>Insurance</t>
-        </is>
-      </c>
-      <c r="D314" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Unrealized (loss)/gain on marketable securities (Note 4)</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr"/>
       <c r="E314" t="inlineStr">
         <is>
           <t>-</t>
@@ -35593,16 +35521,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H314" s="5" t="n">
-        <v>0.043873</v>
+      <c r="H314" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I314" s="5" t="n">
-        <v>0.04176</v>
-      </c>
-      <c r="J314" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.192781</v>
+      </c>
+      <c r="J314" s="5" t="n">
+        <v>-0.008815</v>
       </c>
       <c r="K314" t="inlineStr">
         <is>
@@ -35658,12 +35586,12 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>Depreciation                                                                                                                ‐           28,410</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Legal, audit and accounting</t>
+          <t>Realized (loss)/gain on marketable securities</t>
         </is>
       </c>
       <c r="D315" t="inlineStr"/>
@@ -35682,11 +35610,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H315" s="5" t="n">
-        <v>0.065113</v>
+      <c r="H315" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I315" s="5" t="n">
-        <v>0.046795</v>
+        <v>-0.280597</v>
       </c>
       <c r="J315" t="inlineStr">
         <is>
@@ -35747,12 +35677,12 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>Depreciation                                                                                                                ‐           28,410</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>Management fees and corporate services</t>
+          <t>Gain/(loss) on sale of mineral property (Note 8a)</t>
         </is>
       </c>
       <c r="D316" t="inlineStr"/>
@@ -35771,11 +35701,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H316" s="5" t="n">
-        <v>0.020875</v>
+      <c r="H316" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I316" s="5" t="n">
-        <v>0.11045</v>
+        <v>0.129888</v>
       </c>
       <c r="J316" t="inlineStr">
         <is>
@@ -35836,19 +35768,15 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Depreciation                                                                                                                ‐           28,410</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>Office and miscellaneous</t>
-        </is>
-      </c>
-      <c r="D317" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Write-down of mineral properties (Note 8)</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr"/>
       <c r="E317" t="inlineStr">
         <is>
           <t>-</t>
@@ -35859,21 +35787,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G317" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G317" s="5" t="n">
+        <v>-1.748047</v>
       </c>
       <c r="H317" s="5" t="n">
-        <v>0.043633</v>
-      </c>
-      <c r="I317" s="5" t="n">
-        <v>0.043192</v>
-      </c>
-      <c r="J317" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-8.375658</v>
+      </c>
+      <c r="I317" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J317" s="5" t="n">
+        <v>-0.08058800000000001</v>
       </c>
       <c r="K317" t="inlineStr">
         <is>
@@ -35934,7 +35860,7 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>Regulatory and transfer agent fees</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
@@ -35958,10 +35884,10 @@
         </is>
       </c>
       <c r="H318" s="5" t="n">
-        <v>0.023726</v>
+        <v>0.043873</v>
       </c>
       <c r="I318" s="5" t="n">
-        <v>0.038921</v>
+        <v>0.04176</v>
       </c>
       <c r="J318" t="inlineStr">
         <is>
@@ -36027,14 +35953,10 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>Rent</t>
-        </is>
-      </c>
-      <c r="D319" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Legal, audit and accounting</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr"/>
       <c r="E319" t="inlineStr">
         <is>
           <t>-</t>
@@ -36051,10 +35973,10 @@
         </is>
       </c>
       <c r="H319" s="5" t="n">
-        <v>0.083132</v>
+        <v>0.065113</v>
       </c>
       <c r="I319" s="5" t="n">
-        <v>0.06347999999999999</v>
+        <v>0.046795</v>
       </c>
       <c r="J319" t="inlineStr">
         <is>
@@ -36120,7 +36042,7 @@
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>Share‐based compensation (Note 11d)</t>
+          <t>Management fees and corporate services</t>
         </is>
       </c>
       <c r="D320" t="inlineStr"/>
@@ -36140,10 +36062,10 @@
         </is>
       </c>
       <c r="H320" s="5" t="n">
-        <v>0.087187</v>
+        <v>0.020875</v>
       </c>
       <c r="I320" s="5" t="n">
-        <v>0.04901</v>
+        <v>0.11045</v>
       </c>
       <c r="J320" t="inlineStr">
         <is>
@@ -36209,7 +36131,7 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>Travel</t>
+          <t>Office and miscellaneous</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
@@ -36233,10 +36155,10 @@
         </is>
       </c>
       <c r="H321" s="5" t="n">
-        <v>0.004879</v>
+        <v>0.043633</v>
       </c>
       <c r="I321" s="5" t="n">
-        <v>0.021795</v>
+        <v>0.043192</v>
       </c>
       <c r="J321" t="inlineStr">
         <is>
@@ -36302,10 +36224,14 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>Wages and benefits</t>
-        </is>
-      </c>
-      <c r="D322" t="inlineStr"/>
+          <t>Regulatory and transfer agent fees</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E322" t="inlineStr">
         <is>
           <t>-</t>
@@ -36322,10 +36248,10 @@
         </is>
       </c>
       <c r="H322" s="5" t="n">
-        <v>0.073245</v>
+        <v>0.023726</v>
       </c>
       <c r="I322" s="5" t="n">
-        <v>0.09358900000000001</v>
+        <v>0.038921</v>
       </c>
       <c r="J322" t="inlineStr">
         <is>
@@ -36386,15 +36312,19 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>Property cost/(recovery)                                                                                                 ‐             (4,820)</t>
+          <t>Depreciation                                                                                                                ‐           28,410</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>Exploration expenditures (Note 7)</t>
-        </is>
-      </c>
-      <c r="D323" t="inlineStr"/>
+          <t>Rent</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E323" t="inlineStr">
         <is>
           <t>-</t>
@@ -36411,10 +36341,10 @@
         </is>
       </c>
       <c r="H323" s="5" t="n">
-        <v>0.375087</v>
+        <v>0.083132</v>
       </c>
       <c r="I323" s="5" t="n">
-        <v>0.894221</v>
+        <v>0.06347999999999999</v>
       </c>
       <c r="J323" t="inlineStr">
         <is>
@@ -36475,12 +36405,12 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>Property cost/(recovery)                                                                                                 ‐             (4,820)</t>
+          <t>Depreciation                                                                                                                ‐           28,410</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>Property cost/(recovery)                                                                                                 ‐             (4,820) total</t>
+          <t>Share‐based compensation (Note 11d)</t>
         </is>
       </c>
       <c r="D324" t="inlineStr"/>
@@ -36500,10 +36430,10 @@
         </is>
       </c>
       <c r="H324" s="5" t="n">
-        <v>-0.856069</v>
+        <v>0.087187</v>
       </c>
       <c r="I324" s="5" t="n">
-        <v>-1.51331</v>
+        <v>0.04901</v>
       </c>
       <c r="J324" t="inlineStr">
         <is>
@@ -36564,15 +36494,19 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>Interest income                                                                                                                     ‐            4,406</t>
+          <t>Depreciation                                                                                                                ‐           28,410</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>Unrealized (loss)/gain on marketable securities (Note 5)</t>
-        </is>
-      </c>
-      <c r="D325" t="inlineStr"/>
+          <t>Travel</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E325" t="inlineStr">
         <is>
           <t>-</t>
@@ -36589,10 +36523,10 @@
         </is>
       </c>
       <c r="H325" s="5" t="n">
-        <v>0.09465</v>
+        <v>0.004879</v>
       </c>
       <c r="I325" s="5" t="n">
-        <v>-0.192781</v>
+        <v>0.021795</v>
       </c>
       <c r="J325" t="inlineStr">
         <is>
@@ -36653,12 +36587,12 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>Realized (loss)/gain on marketable securities                                               (280,597)                        ‐</t>
+          <t>Depreciation                                                                                                                ‐           28,410</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>Gain/(loss) on sale of mineral property (Note 7a)</t>
+          <t>Wages and benefits</t>
         </is>
       </c>
       <c r="D326" t="inlineStr"/>
@@ -36678,10 +36612,10 @@
         </is>
       </c>
       <c r="H326" s="5" t="n">
-        <v>0.55535</v>
+        <v>0.073245</v>
       </c>
       <c r="I326" s="5" t="n">
-        <v>0.129888</v>
+        <v>0.09358900000000001</v>
       </c>
       <c r="J326" t="inlineStr">
         <is>
@@ -36742,12 +36676,12 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Flow through premium                                                     200,237                         ‐</t>
+          <t>Property cost/(recovery)                                                                                                 ‐             (4,820)</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>Flow through premium                                                     200,237                         ‐ total</t>
+          <t>Exploration expenditures (Note 7)</t>
         </is>
       </c>
       <c r="D327" t="inlineStr"/>
@@ -36767,10 +36701,10 @@
         </is>
       </c>
       <c r="H327" s="5" t="n">
-        <v>-7.821558</v>
+        <v>0.375087</v>
       </c>
       <c r="I327" s="5" t="n">
-        <v>-0.143253</v>
+        <v>0.894221</v>
       </c>
       <c r="J327" t="inlineStr">
         <is>
@@ -36831,19 +36765,15 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Flow through premium                                                     200,237                         ‐</t>
+          <t>Property cost/(recovery)                                                                                                 ‐             (4,820)</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>Loss and comprehensive loss for the year</t>
-        </is>
-      </c>
-      <c r="D328" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Property cost/(recovery)                                                                                                 ‐             (4,820) total</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr"/>
       <c r="E328" t="inlineStr">
         <is>
           <t>-</t>
@@ -36860,10 +36790,10 @@
         </is>
       </c>
       <c r="H328" s="5" t="n">
-        <v>-8.677626999999999</v>
+        <v>-0.856069</v>
       </c>
       <c r="I328" s="5" t="n">
-        <v>-1.656563</v>
+        <v>-1.51331</v>
       </c>
       <c r="J328" t="inlineStr">
         <is>
@@ -36924,19 +36854,15 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Flow through premium                                                     200,237                         ‐</t>
+          <t>Interest income                                                                                                                     ‐            4,406</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>Basic and diluted loss per common share $</t>
-        </is>
-      </c>
-      <c r="D329" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
+          <t>Unrealized (loss)/gain on marketable securities (Note 5)</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr"/>
       <c r="E329" t="inlineStr">
         <is>
           <t>-</t>
@@ -36953,10 +36879,10 @@
         </is>
       </c>
       <c r="H329" s="5" t="n">
-        <v>-1.7e-07</v>
+        <v>0.09465</v>
       </c>
       <c r="I329" s="5" t="n">
-        <v>-3e-08</v>
+        <v>-0.192781</v>
       </c>
       <c r="J329" t="inlineStr">
         <is>
@@ -37017,33 +36943,35 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Realized (loss)/gain on marketable securities                                               (280,597)                        ‐</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>Business development $</t>
+          <t>Gain/(loss) on sale of mineral property (Note 7a)</t>
         </is>
       </c>
       <c r="D330" t="inlineStr"/>
-      <c r="E330" s="5" t="n">
-        <v>0.053193</v>
-      </c>
-      <c r="F330" s="5" t="n">
-        <v>0.016385</v>
-      </c>
-      <c r="G330" s="5" t="n">
-        <v>0.00678</v>
-      </c>
-      <c r="H330" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I330" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E330" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F330" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G330" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H330" s="5" t="n">
+        <v>0.55535</v>
+      </c>
+      <c r="I330" s="5" t="n">
+        <v>0.129888</v>
       </c>
       <c r="J330" t="inlineStr">
         <is>
@@ -37104,37 +37032,35 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Flow through premium                                                     200,237                         ‐</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>Depreciation</t>
-        </is>
-      </c>
-      <c r="D331" t="inlineStr">
-        <is>
-          <t>Depreciation</t>
-        </is>
-      </c>
-      <c r="E331" s="5" t="n">
-        <v>0.069158</v>
-      </c>
-      <c r="F331" s="5" t="n">
-        <v>0.052764</v>
-      </c>
-      <c r="G331" s="5" t="n">
-        <v>0.037529</v>
-      </c>
-      <c r="H331" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I331" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Flow through premium                                                     200,237                         ‐ total</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr"/>
+      <c r="E331" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F331" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G331" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H331" s="5" t="n">
+        <v>-7.821558</v>
+      </c>
+      <c r="I331" s="5" t="n">
+        <v>-0.143253</v>
       </c>
       <c r="J331" t="inlineStr">
         <is>
@@ -37195,37 +37121,39 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Flow through premium                                                     200,237                         ‐</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Loss and comprehensive loss for the year</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E332" s="5" t="n">
-        <v>0.063788</v>
-      </c>
-      <c r="F332" s="5" t="n">
-        <v>0.05197</v>
-      </c>
-      <c r="G332" s="5" t="n">
-        <v>0.042998</v>
-      </c>
-      <c r="H332" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I332" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F332" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G332" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H332" s="5" t="n">
+        <v>-8.677626999999999</v>
+      </c>
+      <c r="I332" s="5" t="n">
+        <v>-1.656563</v>
       </c>
       <c r="J332" t="inlineStr">
         <is>
@@ -37286,33 +37214,39 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Flow through premium                                                     200,237                         ‐</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>Legal, audit and accounting</t>
-        </is>
-      </c>
-      <c r="D333" t="inlineStr"/>
-      <c r="E333" s="5" t="n">
-        <v>0.130389</v>
-      </c>
-      <c r="F333" s="5" t="n">
-        <v>0.06451999999999999</v>
-      </c>
-      <c r="G333" s="5" t="n">
-        <v>0.03307</v>
-      </c>
-      <c r="H333" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I333" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Basic and diluted loss per common share $</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E333" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F333" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G333" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H333" s="5" t="n">
+        <v>-1.7e-07</v>
+      </c>
+      <c r="I333" s="5" t="n">
+        <v>-3e-08</v>
       </c>
       <c r="J333" t="inlineStr">
         <is>
@@ -37373,28 +37307,34 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>Management fees and corporate services</t>
-        </is>
-      </c>
-      <c r="D334" t="inlineStr"/>
-      <c r="E334" s="5" t="n">
-        <v>0.289714</v>
-      </c>
-      <c r="F334" s="5" t="n">
-        <v>0.025225</v>
+          <t>Depreciation</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>Depreciation</t>
+        </is>
+      </c>
+      <c r="E334" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F334" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G334" s="5" t="n">
-        <v>0.01791</v>
-      </c>
-      <c r="H334" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.037529</v>
+      </c>
+      <c r="H334" s="5" t="n">
+        <v>0.02841</v>
       </c>
       <c r="I334" t="inlineStr">
         <is>
@@ -37460,32 +37400,32 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>Office and miscellaneous</t>
-        </is>
-      </c>
-      <c r="D335" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E335" s="5" t="n">
-        <v>0.14589</v>
-      </c>
-      <c r="F335" s="5" t="n">
-        <v>0.087536</v>
-      </c>
-      <c r="G335" s="5" t="n">
-        <v>0.037709</v>
-      </c>
-      <c r="H335" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Share-based compensation (Note 11)</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr"/>
+      <c r="E335" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F335" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G335" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H335" s="5" t="n">
+        <v>0.087187</v>
       </c>
       <c r="I335" t="inlineStr">
         <is>
@@ -37551,32 +37491,32 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>Regulatory and transfer agent fees</t>
-        </is>
-      </c>
-      <c r="D336" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E336" s="5" t="n">
-        <v>0.049478</v>
-      </c>
-      <c r="F336" s="5" t="n">
-        <v>0.024922</v>
-      </c>
-      <c r="G336" s="5" t="n">
-        <v>0.028252</v>
-      </c>
-      <c r="H336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Property Cost/(recovery)</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr"/>
+      <c r="E336" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F336" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G336" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H336" s="5" t="n">
+        <v>-0.00482</v>
       </c>
       <c r="I336" t="inlineStr">
         <is>
@@ -37642,27 +37582,27 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>Rent</t>
-        </is>
-      </c>
-      <c r="D337" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E337" s="5" t="n">
-        <v>0.178471</v>
-      </c>
-      <c r="F337" s="5" t="n">
-        <v>0.114896</v>
+          <t>Recovery of previous write-downs</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr"/>
+      <c r="E337" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F337" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G337" s="5" t="n">
-        <v>0.11512</v>
+        <v>0.262949</v>
       </c>
       <c r="H337" t="inlineStr">
         <is>
@@ -37733,32 +37673,32 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>Travel</t>
-        </is>
-      </c>
-      <c r="D338" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E338" s="5" t="n">
-        <v>0.020924</v>
-      </c>
-      <c r="F338" s="5" t="n">
-        <v>0.008307999999999999</v>
-      </c>
-      <c r="G338" s="5" t="n">
-        <v>0.008534999999999999</v>
-      </c>
-      <c r="H338" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Gain on sale of mineral properties (Note 8)</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr"/>
+      <c r="E338" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F338" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G338" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H338" s="5" t="n">
+        <v>0.55535</v>
       </c>
       <c r="I338" t="inlineStr">
         <is>
@@ -37824,23 +37764,27 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>Wages and benefits</t>
+          <t>Write-down of exploration deposits</t>
         </is>
       </c>
       <c r="D339" t="inlineStr"/>
-      <c r="E339" s="5" t="n">
-        <v>0.249389</v>
-      </c>
-      <c r="F339" s="5" t="n">
-        <v>0.180344</v>
+      <c r="E339" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F339" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G339" s="5" t="n">
-        <v>0.104102</v>
+        <v>-0.03</v>
       </c>
       <c r="H339" t="inlineStr">
         <is>
@@ -37911,12 +37855,12 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>Exploration expenditures (Note 7)</t>
+          <t>Write-down of equipment (Note 6)</t>
         </is>
       </c>
       <c r="D340" t="inlineStr"/>
@@ -37925,16 +37869,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F340" s="5" t="n">
-        <v>0.28118</v>
-      </c>
-      <c r="G340" s="5" t="n">
-        <v>0.44555</v>
-      </c>
-      <c r="H340" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F340" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G340" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H340" s="5" t="n">
+        <v>-0.100306</v>
       </c>
       <c r="I340" t="inlineStr">
         <is>
@@ -38000,34 +37946,32 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>EXPENSES total</t>
-        </is>
-      </c>
-      <c r="D341" t="inlineStr">
-        <is>
-          <t>OperatingExpense</t>
-        </is>
-      </c>
+          <t>Unrealized (loss)/gain on marketable securities (Note 5)</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr"/>
       <c r="E341" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F341" s="5" t="n">
-        <v>0.90805</v>
-      </c>
-      <c r="G341" s="5" t="n">
-        <v>0.877555</v>
-      </c>
-      <c r="H341" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F341" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G341" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H341" s="5" t="n">
+        <v>0.09465</v>
       </c>
       <c r="I341" t="inlineStr">
         <is>
@@ -38098,24 +38042,18 @@
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>Interest income</t>
-        </is>
-      </c>
-      <c r="D342" t="inlineStr">
-        <is>
-          <t>InterestIncomeNonOperating</t>
-        </is>
-      </c>
-      <c r="E342" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Business development $</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr"/>
+      <c r="E342" s="5" t="n">
+        <v>0.053193</v>
       </c>
       <c r="F342" s="5" t="n">
-        <v>0.001534</v>
+        <v>0.016385</v>
       </c>
       <c r="G342" s="5" t="n">
-        <v>0.013911</v>
+        <v>0.00678</v>
       </c>
       <c r="H342" t="inlineStr">
         <is>
@@ -38191,22 +38129,22 @@
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>Recovery of previous write-downs</t>
-        </is>
-      </c>
-      <c r="D343" t="inlineStr"/>
-      <c r="E343" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F343" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Depreciation</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>Depreciation</t>
+        </is>
+      </c>
+      <c r="E343" s="5" t="n">
+        <v>0.069158</v>
+      </c>
+      <c r="F343" s="5" t="n">
+        <v>0.052764</v>
       </c>
       <c r="G343" s="5" t="n">
-        <v>0.262949</v>
+        <v>0.037529</v>
       </c>
       <c r="H343" t="inlineStr">
         <is>
@@ -38282,22 +38220,22 @@
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>Write-off of exploration deposits</t>
-        </is>
-      </c>
-      <c r="D344" t="inlineStr"/>
-      <c r="E344" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F344" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Insurance</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E344" s="5" t="n">
+        <v>0.063788</v>
+      </c>
+      <c r="F344" s="5" t="n">
+        <v>0.05197</v>
       </c>
       <c r="G344" s="5" t="n">
-        <v>-0.03</v>
+        <v>0.042998</v>
       </c>
       <c r="H344" t="inlineStr">
         <is>
@@ -38373,20 +38311,18 @@
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>Write-off of mineral properties (Note 7)</t>
+          <t>Legal, audit and accounting</t>
         </is>
       </c>
       <c r="D345" t="inlineStr"/>
-      <c r="E345" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E345" s="5" t="n">
+        <v>0.130389</v>
       </c>
       <c r="F345" s="5" t="n">
-        <v>-0.403033</v>
+        <v>0.06451999999999999</v>
       </c>
       <c r="G345" s="5" t="n">
-        <v>-1.748047</v>
+        <v>0.03307</v>
       </c>
       <c r="H345" t="inlineStr">
         <is>
@@ -38462,24 +38398,18 @@
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>Loss and comprehensive loss for the year $</t>
-        </is>
-      </c>
-      <c r="D346" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
-      <c r="E346" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Management fees and corporate services</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr"/>
+      <c r="E346" s="5" t="n">
+        <v>0.289714</v>
       </c>
       <c r="F346" s="5" t="n">
-        <v>-1.309549</v>
+        <v>0.025225</v>
       </c>
       <c r="G346" s="5" t="n">
-        <v>-2.378742</v>
+        <v>0.01791</v>
       </c>
       <c r="H346" t="inlineStr">
         <is>
@@ -38555,24 +38485,22 @@
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>Basic and diluted loss per common share $</t>
+          <t>Office and miscellaneous</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
-      <c r="E347" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E347" s="5" t="n">
+        <v>0.14589</v>
       </c>
       <c r="F347" s="5" t="n">
-        <v>-4e-08</v>
+        <v>0.087536</v>
       </c>
       <c r="G347" s="5" t="n">
-        <v>-5e-08</v>
+        <v>0.037709</v>
       </c>
       <c r="H347" t="inlineStr">
         <is>
@@ -38648,22 +38576,22 @@
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>Share-based compensation (Note 10)</t>
-        </is>
-      </c>
-      <c r="D348" t="inlineStr"/>
+          <t>Regulatory and transfer agent fees</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E348" s="5" t="n">
-        <v>0.291944</v>
-      </c>
-      <c r="F348" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G348" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.049478</v>
+      </c>
+      <c r="F348" s="5" t="n">
+        <v>0.024922</v>
+      </c>
+      <c r="G348" s="5" t="n">
+        <v>0.028252</v>
       </c>
       <c r="H348" t="inlineStr">
         <is>
@@ -38739,22 +38667,22 @@
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>Expense recovery</t>
-        </is>
-      </c>
-      <c r="D349" t="inlineStr"/>
+          <t>Rent</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E349" s="5" t="n">
-        <v>-0.060704</v>
-      </c>
-      <c r="F349" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G349" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.178471</v>
+      </c>
+      <c r="F349" s="5" t="n">
+        <v>0.114896</v>
+      </c>
+      <c r="G349" s="5" t="n">
+        <v>0.11512</v>
       </c>
       <c r="H349" t="inlineStr">
         <is>
@@ -38830,24 +38758,22 @@
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>Loss before other items</t>
+          <t>Travel</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>OperatingIncome</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E350" s="5" t="n">
-        <v>-1.481634</v>
+        <v>0.020924</v>
       </c>
       <c r="F350" s="5" t="n">
-        <v>-0.626869</v>
-      </c>
-      <c r="G350" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.008307999999999999</v>
+      </c>
+      <c r="G350" s="5" t="n">
+        <v>0.008534999999999999</v>
       </c>
       <c r="H350" t="inlineStr">
         <is>
@@ -38918,29 +38844,23 @@
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>OTHER ITEMS</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>Interest income</t>
-        </is>
-      </c>
-      <c r="D351" t="inlineStr">
-        <is>
-          <t>InterestIncomeNonOperating</t>
-        </is>
-      </c>
+          <t>Wages and benefits</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr"/>
       <c r="E351" s="5" t="n">
-        <v>0.029443</v>
+        <v>0.249389</v>
       </c>
       <c r="F351" s="5" t="n">
-        <v>0.001535</v>
-      </c>
-      <c r="G351" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.180344</v>
+      </c>
+      <c r="G351" s="5" t="n">
+        <v>0.104102</v>
       </c>
       <c r="H351" t="inlineStr">
         <is>
@@ -39011,25 +38931,25 @@
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>OTHER ITEMS</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>Write-off of mineral properties (Note 7)</t>
+          <t>Exploration expenditures (Note 7)</t>
         </is>
       </c>
       <c r="D352" t="inlineStr"/>
-      <c r="E352" s="5" t="n">
-        <v>-40.968246</v>
+      <c r="E352" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F352" s="5" t="n">
-        <v>-0.557357</v>
-      </c>
-      <c r="G352" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.28118</v>
+      </c>
+      <c r="G352" s="5" t="n">
+        <v>0.44555</v>
       </c>
       <c r="H352" t="inlineStr">
         <is>
@@ -39100,25 +39020,29 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>OTHER ITEMS</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>OTHER ITEMS total</t>
-        </is>
-      </c>
-      <c r="D353" t="inlineStr"/>
-      <c r="E353" s="5" t="n">
-        <v>-40.938803</v>
+          <t>EXPENSES total</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
+      <c r="E353" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F353" s="5" t="n">
-        <v>-0.555822</v>
-      </c>
-      <c r="G353" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.90805</v>
+      </c>
+      <c r="G353" s="5" t="n">
+        <v>0.877555</v>
       </c>
       <c r="H353" t="inlineStr">
         <is>
@@ -39189,29 +39113,29 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>OTHER ITEMS</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>Loss before income tax</t>
+          <t>Interest income</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>PretaxIncome</t>
-        </is>
-      </c>
-      <c r="E354" s="5" t="n">
-        <v>-42.420437</v>
+          <t>InterestIncomeNonOperating</t>
+        </is>
+      </c>
+      <c r="E354" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F354" s="5" t="n">
-        <v>-1.182691</v>
-      </c>
-      <c r="G354" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.001534</v>
+      </c>
+      <c r="G354" s="5" t="n">
+        <v>0.013911</v>
       </c>
       <c r="H354" t="inlineStr">
         <is>
@@ -39282,27 +39206,27 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>OTHER ITEMS</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>Deferred income tax recovery (Note 15)</t>
+          <t>Recovery of previous write-downs</t>
         </is>
       </c>
       <c r="D355" t="inlineStr"/>
-      <c r="E355" s="5" t="n">
-        <v>0.737</v>
+      <c r="E355" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F355" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G355" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G355" s="5" t="n">
+        <v>0.262949</v>
       </c>
       <c r="H355" t="inlineStr">
         <is>
@@ -39373,29 +39297,27 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>OTHER ITEMS</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>Loss and comprehensive loss for the year $</t>
-        </is>
-      </c>
-      <c r="D356" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
-      <c r="E356" s="5" t="n">
-        <v>-41.683437</v>
-      </c>
-      <c r="F356" s="5" t="n">
-        <v>-1.182691</v>
-      </c>
-      <c r="G356" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Write-off of exploration deposits</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr"/>
+      <c r="E356" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F356" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G356" s="5" t="n">
+        <v>-0.03</v>
       </c>
       <c r="H356" t="inlineStr">
         <is>
@@ -39466,86 +39388,1188 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>Write-off of mineral properties (Note 7)</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr"/>
+      <c r="E357" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F357" s="5" t="n">
+        <v>-0.403033</v>
+      </c>
+      <c r="G357" s="5" t="n">
+        <v>-1.748047</v>
+      </c>
+      <c r="H357" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I357" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J357" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K357" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L357" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M357" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N357" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O357" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P357" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q357" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R357" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S357" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>Loss and comprehensive loss for the year $</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E358" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F358" s="5" t="n">
+        <v>-1.309549</v>
+      </c>
+      <c r="G358" s="5" t="n">
+        <v>-2.378742</v>
+      </c>
+      <c r="H358" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I358" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J358" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K358" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L358" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M358" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N358" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O358" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P358" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q358" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R358" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S358" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>Basic and diluted loss per common share $</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E359" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F359" s="5" t="n">
+        <v>-4e-08</v>
+      </c>
+      <c r="G359" s="5" t="n">
+        <v>-5e-08</v>
+      </c>
+      <c r="H359" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I359" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J359" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K359" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L359" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M359" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N359" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O359" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P359" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q359" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R359" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S359" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>Share-based compensation (Note 10)</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr"/>
+      <c r="E360" s="5" t="n">
+        <v>0.291944</v>
+      </c>
+      <c r="F360" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G360" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H360" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I360" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J360" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K360" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L360" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M360" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N360" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O360" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P360" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q360" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R360" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S360" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>Expense recovery</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr"/>
+      <c r="E361" s="5" t="n">
+        <v>-0.060704</v>
+      </c>
+      <c r="F361" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G361" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H361" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I361" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J361" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K361" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L361" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M361" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N361" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O361" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P361" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q361" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R361" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S361" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>Loss before other items</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>OperatingIncome</t>
+        </is>
+      </c>
+      <c r="E362" s="5" t="n">
+        <v>-1.481634</v>
+      </c>
+      <c r="F362" s="5" t="n">
+        <v>-0.626869</v>
+      </c>
+      <c r="G362" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H362" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I362" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J362" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K362" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L362" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M362" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N362" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O362" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P362" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q362" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R362" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S362" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
           <t>OTHER ITEMS</t>
         </is>
       </c>
-      <c r="C357" t="inlineStr">
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>Interest income</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>InterestIncomeNonOperating</t>
+        </is>
+      </c>
+      <c r="E363" s="5" t="n">
+        <v>0.029443</v>
+      </c>
+      <c r="F363" s="5" t="n">
+        <v>0.001535</v>
+      </c>
+      <c r="G363" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H363" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I363" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J363" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K363" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L363" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M363" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N363" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O363" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P363" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q363" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R363" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S363" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>OTHER ITEMS</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>Write-off of mineral properties (Note 7)</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr"/>
+      <c r="E364" s="5" t="n">
+        <v>-40.968246</v>
+      </c>
+      <c r="F364" s="5" t="n">
+        <v>-0.557357</v>
+      </c>
+      <c r="G364" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H364" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I364" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J364" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K364" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L364" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M364" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N364" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O364" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P364" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q364" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R364" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S364" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>OTHER ITEMS</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>OTHER ITEMS total</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr"/>
+      <c r="E365" s="5" t="n">
+        <v>-40.938803</v>
+      </c>
+      <c r="F365" s="5" t="n">
+        <v>-0.555822</v>
+      </c>
+      <c r="G365" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H365" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I365" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J365" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K365" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L365" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M365" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N365" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O365" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P365" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q365" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R365" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S365" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>OTHER ITEMS</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>Loss before income tax</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>PretaxIncome</t>
+        </is>
+      </c>
+      <c r="E366" s="5" t="n">
+        <v>-42.420437</v>
+      </c>
+      <c r="F366" s="5" t="n">
+        <v>-1.182691</v>
+      </c>
+      <c r="G366" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H366" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I366" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J366" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K366" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L366" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M366" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N366" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O366" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P366" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q366" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R366" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S366" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>OTHER ITEMS</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>Deferred income tax recovery (Note 15)</t>
+        </is>
+      </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
+      <c r="E367" s="5" t="n">
+        <v>0.737</v>
+      </c>
+      <c r="F367" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G367" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H367" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I367" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J367" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K367" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L367" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M367" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N367" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O367" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P367" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q367" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R367" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S367" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>OTHER ITEMS</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>Loss and comprehensive loss for the year $</t>
+        </is>
+      </c>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E368" s="5" t="n">
+        <v>-41.683437</v>
+      </c>
+      <c r="F368" s="5" t="n">
+        <v>-1.182691</v>
+      </c>
+      <c r="G368" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H368" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I368" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J368" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K368" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L368" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M368" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N368" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O368" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P368" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q368" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R368" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S368" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>OTHER ITEMS</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
         <is>
           <t>Basic and diluted loss per common share (Note 13) $</t>
         </is>
       </c>
-      <c r="D357" t="inlineStr">
+      <c r="D369" t="inlineStr">
         <is>
           <t>BasicEPS</t>
         </is>
       </c>
-      <c r="E357" s="5" t="n">
+      <c r="E369" s="5" t="n">
         <v>-1.17e-06</v>
       </c>
-      <c r="F357" s="5" t="n">
+      <c r="F369" s="5" t="n">
         <v>-3e-08</v>
       </c>
-      <c r="G357" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H357" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I357" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J357" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K357" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L357" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M357" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N357" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O357" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P357" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q357" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R357" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S357" t="inlineStr">
+      <c r="G369" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H369" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I369" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J369" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K369" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L369" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M369" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N369" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O369" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P369" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q369" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R369" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S369" t="inlineStr">
         <is>
           <t>-</t>
         </is>
